--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tasks" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'tasks'!$A$1:$X$129</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -459,11 +461,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X129"/>
+  <dimension ref="A1:X135"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="19.6640625" customWidth="1" min="2" max="4"/>
@@ -1200,7 +1202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="1">
       <c r="A11" t="n">
         <v>4</v>
       </c>
@@ -1264,7 +1266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="1">
       <c r="A12" t="n">
         <v>5</v>
       </c>
@@ -1318,7 +1320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="1">
       <c r="A13" t="n">
         <v>6</v>
       </c>
@@ -1372,7 +1374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="1">
       <c r="A14" t="n">
         <v>7</v>
       </c>
@@ -1426,7 +1428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="1">
       <c r="A15" t="n">
         <v>8</v>
       </c>
@@ -1480,7 +1482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="1">
       <c r="A16" t="n">
         <v>9</v>
       </c>
@@ -1531,7 +1533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="1">
       <c r="A17" t="n">
         <v>10</v>
       </c>
@@ -1582,7 +1584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="1">
       <c r="A18" t="n">
         <v>11</v>
       </c>
@@ -1633,7 +1635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="1">
       <c r="A19" t="n">
         <v>12</v>
       </c>
@@ -1684,7 +1686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="1">
       <c r="A20" t="n">
         <v>13</v>
       </c>
@@ -1735,7 +1737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="1">
       <c r="A21" t="n">
         <v>14</v>
       </c>
@@ -1786,7 +1788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="1">
       <c r="A22" t="n">
         <v>15</v>
       </c>
@@ -1837,7 +1839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="1">
       <c r="A23" t="n">
         <v>16</v>
       </c>
@@ -1888,7 +1890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="1">
       <c r="A24" t="n">
         <v>17</v>
       </c>
@@ -1939,7 +1941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="1">
       <c r="A25" t="n">
         <v>18</v>
       </c>
@@ -1990,7 +1992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="1">
       <c r="A26" t="n">
         <v>19</v>
       </c>
@@ -2029,7 +2031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="1">
       <c r="A27" t="n">
         <v>20</v>
       </c>
@@ -4410,7 +4412,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>exxon</t>
+          <t>exxon aceite</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4550,7 +4552,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stp</t>
+          <t>aceite stp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4620,7 +4622,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>motul</t>
+          <t>aceite motul</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4779,7 +4781,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L66" t="b">
         <v>1</v>
@@ -4830,7 +4832,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>akron</t>
+          <t>akron aceite</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5087,7 +5089,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="1">
       <c r="A71" t="inlineStr">
         <is>
           <t>65</t>
@@ -5155,7 +5157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="1">
       <c r="A72" t="inlineStr">
         <is>
           <t>66</t>
@@ -5223,7 +5225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="1">
       <c r="A73" t="inlineStr">
         <is>
           <t>67</t>
@@ -5291,7 +5293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="1">
       <c r="A74" t="inlineStr">
         <is>
           <t>68</t>
@@ -5359,7 +5361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="1">
       <c r="A75" t="inlineStr">
         <is>
           <t>69</t>
@@ -5427,7 +5429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="1">
       <c r="A76" t="inlineStr">
         <is>
           <t>70</t>
@@ -5495,7 +5497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="1">
       <c r="A77" t="inlineStr">
         <is>
           <t>71</t>
@@ -5563,7 +5565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="1">
       <c r="A78" t="inlineStr">
         <is>
           <t>72</t>
@@ -5631,7 +5633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="1">
       <c r="A79" t="inlineStr">
         <is>
           <t>73</t>
@@ -5699,7 +5701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="1">
       <c r="A80" t="inlineStr">
         <is>
           <t>74</t>
@@ -5767,7 +5769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="1">
       <c r="A81" t="inlineStr">
         <is>
           <t>75</t>
@@ -5835,7 +5837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="1">
       <c r="A82" t="inlineStr">
         <is>
           <t>76</t>
@@ -5903,7 +5905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="1">
       <c r="A83" t="inlineStr">
         <is>
           <t>77</t>
@@ -5971,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="1">
       <c r="A84" t="inlineStr">
         <is>
           <t>78</t>
@@ -6039,7 +6041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="1">
       <c r="A85" t="inlineStr">
         <is>
           <t>79</t>
@@ -6107,7 +6109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="1">
       <c r="A86" t="n">
         <v>80</v>
       </c>
@@ -6158,7 +6160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="1">
       <c r="A87" t="n">
         <v>81</v>
       </c>
@@ -6212,7 +6214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="1">
       <c r="A88" t="n">
         <v>82</v>
       </c>
@@ -6266,7 +6268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="1">
       <c r="A89" t="n">
         <v>83</v>
       </c>
@@ -6320,7 +6322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="1">
       <c r="A90" t="n">
         <v>84</v>
       </c>
@@ -6381,7 +6383,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="1">
       <c r="A91" t="n">
         <v>85</v>
       </c>
@@ -6445,7 +6447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="1">
       <c r="A92" t="n">
         <v>86</v>
       </c>
@@ -6506,7 +6508,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="1">
       <c r="A93" t="n">
         <v>87</v>
       </c>
@@ -6570,7 +6572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="1">
       <c r="A94" t="n">
         <v>88</v>
       </c>
@@ -6627,7 +6629,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="1">
       <c r="A95" t="n">
         <v>89</v>
       </c>
@@ -6691,7 +6693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="1">
       <c r="A96" t="n">
         <v>90</v>
       </c>
@@ -6755,7 +6757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="1">
       <c r="A97" t="n">
         <v>91</v>
       </c>
@@ -6819,7 +6821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="1">
       <c r="A98" t="n">
         <v>92</v>
       </c>
@@ -6871,7 +6873,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="1">
       <c r="A99" t="n">
         <v>93</v>
       </c>
@@ -6923,7 +6925,7 @@
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="1">
       <c r="A100" t="n">
         <v>94</v>
       </c>
@@ -6975,7 +6977,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="1">
       <c r="A101" s="2" t="n">
         <v>95</v>
       </c>
@@ -7036,7 +7038,7 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="1">
       <c r="A102" t="n">
         <v>96</v>
       </c>
@@ -7100,7 +7102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="1">
       <c r="A103" t="n">
         <v>97</v>
       </c>
@@ -7159,7 +7161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="1">
       <c r="A104" t="n">
         <v>98</v>
       </c>
@@ -7223,7 +7225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="1">
       <c r="A105" t="n">
         <v>99</v>
       </c>
@@ -7292,7 +7294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="1">
       <c r="A106" t="n">
         <v>100</v>
       </c>
@@ -7350,7 +7352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="1">
       <c r="A107" t="n">
         <v>101</v>
       </c>
@@ -7424,7 +7426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="1">
       <c r="A108" t="n">
         <v>102</v>
       </c>
@@ -7482,7 +7484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="1">
       <c r="A109" t="n">
         <v>103</v>
       </c>
@@ -7556,7 +7558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="1">
       <c r="A110" t="n">
         <v>104</v>
       </c>
@@ -7614,7 +7616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="1">
       <c r="A111" t="n">
         <v>105</v>
       </c>
@@ -7688,7 +7690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="1">
       <c r="A112" t="n">
         <v>106</v>
       </c>
@@ -7760,7 +7762,7 @@
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="1">
       <c r="A113" t="n">
         <v>107</v>
       </c>
@@ -7832,7 +7834,7 @@
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="1">
       <c r="A114" t="n">
         <v>108</v>
       </c>
@@ -7904,7 +7906,7 @@
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="1">
       <c r="A115" t="n">
         <v>109</v>
       </c>
@@ -7976,7 +7978,7 @@
         </is>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="1">
       <c r="A116" t="n">
         <v>110</v>
       </c>
@@ -8048,7 +8050,7 @@
         </is>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="1">
       <c r="A117" t="n">
         <v>111</v>
       </c>
@@ -8120,7 +8122,7 @@
         </is>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="1">
       <c r="A118" t="n">
         <v>112</v>
       </c>
@@ -8192,7 +8194,7 @@
         </is>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="1">
       <c r="A119" t="n">
         <v>113</v>
       </c>
@@ -8264,7 +8266,7 @@
         </is>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="1">
       <c r="A120" t="n">
         <v>114</v>
       </c>
@@ -8336,7 +8338,7 @@
         </is>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="1">
       <c r="A121" t="n">
         <v>115</v>
       </c>
@@ -8407,7 +8409,7 @@
         </is>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="1">
       <c r="A122" t="n">
         <v>116</v>
       </c>
@@ -8481,7 +8483,7 @@
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="1">
       <c r="A123" t="n">
         <v>117</v>
       </c>
@@ -8550,7 +8552,7 @@
         </is>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="1">
       <c r="A124" t="n">
         <v>118</v>
       </c>
@@ -8614,7 +8616,7 @@
         </is>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="1">
       <c r="A125" t="n">
         <v>119</v>
       </c>
@@ -8678,7 +8680,7 @@
         </is>
       </c>
     </row>
-    <row r="126">
+    <row r="126" hidden="1">
       <c r="A126" t="n">
         <v>120</v>
       </c>
@@ -8742,7 +8744,7 @@
         </is>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="1">
       <c r="A127" t="n">
         <v>121</v>
       </c>
@@ -8772,7 +8774,7 @@
         </is>
       </c>
     </row>
-    <row r="128">
+    <row r="128" hidden="1">
       <c r="A128" t="n">
         <v>122</v>
       </c>
@@ -8836,7 +8838,7 @@
         </is>
       </c>
     </row>
-    <row r="129">
+    <row r="129" hidden="1">
       <c r="A129" t="n">
         <v>123</v>
       </c>
@@ -8899,7 +8901,386 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>gd1</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>google_news</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>totalenergies_guadalupe</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Guadalupe seizure news</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>huachicol guadalupe</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>30</v>
+      </c>
+      <c r="L130" t="b">
+        <v>1</v>
+      </c>
+      <c r="M130" t="b">
+        <v>1</v>
+      </c>
+      <c r="N130" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>{"timeframe":"1d","enrich":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>gd2</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>totalenergies_guadalupe</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Guadalupe seizure FB 1</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>huachicol guadalupe</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>30</v>
+      </c>
+      <c r="L131" t="b">
+        <v>1</v>
+      </c>
+      <c r="M131" t="b">
+        <v>1</v>
+      </c>
+      <c r="N131" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>gd3</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>totalenergies_guadalupe</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Guadalupe seizure FB 2</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>huachicol nuevo león</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>30</v>
+      </c>
+      <c r="L132" t="b">
+        <v>1</v>
+      </c>
+      <c r="M132" t="b">
+        <v>1</v>
+      </c>
+      <c r="N132" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>gd4</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>twitter_keyword_search</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>totalenergies_guadalupe</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Guadalupe seizure X 1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>huachicol,guadalupe</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>30</v>
+      </c>
+      <c r="L133" t="b">
+        <v>1</v>
+      </c>
+      <c r="M133" t="b">
+        <v>1</v>
+      </c>
+      <c r="N133" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
+        </is>
+      </c>
+      <c r="T133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>gd5</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>twitter_keyword_search</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>totalenergies_guadalupe</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Guadalupe seizure X 2</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>huachicol,nuevo león</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>30</v>
+      </c>
+      <c r="L134" t="b">
+        <v>1</v>
+      </c>
+      <c r="M134" t="b">
+        <v>1</v>
+      </c>
+      <c r="N134" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
+        </is>
+      </c>
+      <c r="T134" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>124</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>orizaba</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>El Chirimoyo - Search</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>el chirimoyo orizaba</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>50</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que hablen del humedal, laguna o vaso regulador El Chirimoyo en Orizaba, Veracruz: su limpieza, el conflicto entre vecinos y el Ayuntamiento de Orizaba, amparos y resoluciones judiciales, Profepa, el lirio, la fauna o incidentes en el lugar. Elimina publicaciones sobre otros lugares llamados Chirimoyo (colonias o calles de otras ciudades) y las que mencionen Orizaba sin relación con El Chirimoyo.</t>
+        </is>
+      </c>
+      <c r="S135" t="n">
+        <v>1</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>{"enrich_author_after_likes": 50}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:X129">
+    <filterColumn colId="2" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="totalenergies"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="11" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="TRUE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId2"/>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X135"/>
+  <dimension ref="A1:X155"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="19.6640625" customWidth="1" min="2" max="4"/>
@@ -9266,6 +9266,1064 @@
         <is>
           <t>{"enrich_author_after_likes": 50}</t>
         </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>125</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Morelia keyword (round 1, discovery)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>morelia</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Morelia, Michoacán, México (seguridad, gobierno municipal o estatal, obras públicas, servicios como agua, basura, alumbrado, baches, movilidad y transporte, política y partidos, eventos y protestas, economía local, colonias y comunidades). Elimina: promoción de negocios, ventas y rentas, anuncios comerciales, saludos, publicaciones personales sin relevancia pública, y publicaciones que se refieran a otros lugares o cosas llamadas Morelia (calles llamadas Morelia en otras ciudades, el equipo de fútbol Atlético Morelia salvo que el tema sea de interés público local, Morelia como nombre de persona).</t>
+        </is>
+      </c>
+      <c r="S136" t="n">
+        <v>1</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>{"recent_posts": false, "enrich_author_after_likes": 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>126</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Morelia keyword variants (round 1c, discovery)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>morelia michoacán,ayuntamiento de morelia,gobierno de morelia,alfonso martínez morelia, morelia colonia,morelia baches,morelia agua,ooapas morelia,morelia obras, morelia seguridad,morelia policía,morelia transporte,morelia combis, morelia manifestación,morelia bloqueo,morelia bedolla,morelia morena,morelia pan, morelia tenencia,morelia alumbrado,morelia basura,morelia lluvias,morelia mercado, morelia vecinos,morelia centro histórico</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>100</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Morelia, Michoacán, México (seguridad, gobierno municipal o estatal, obras públicas, servicios como agua, basura, alumbrado, baches, movilidad y transporte, política y partidos, eventos y protestas, economía local, colonias y comunidades). Elimina: promoción de negocios, ventas y rentas, anuncios comerciales, saludos, publicaciones personales sin relevancia pública, y publicaciones que se refieran a otros lugares o cosas llamadas Morelia (calles llamadas Morelia en otras ciudades, el equipo de fútbol Atlético Morelia salvo que el tema sea de interés público local, Morelia como nombre de persona).</t>
+        </is>
+      </c>
+      <c r="S137" t="n">
+        <v>1</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>{"enrich_author_after_likes": 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>127</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Gobierno de Morelia</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MoreliaGob</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>100</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>15</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1</v>
+      </c>
+      <c r="X138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Alfonso Martínez Alcázar (alcalde)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AlfonsoMtz.Mx</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>50</v>
+      </c>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>15</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1</v>
+      </c>
+      <c r="X139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>129</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>OOAPAS Morelia</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MoreliaOoapas</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>50</v>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>15</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>1</v>
+      </c>
+      <c r="X140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>130</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Policía de Morelia</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/policiademorelia</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>50</v>
+      </c>
+      <c r="L141" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>15</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>1</v>
+      </c>
+      <c r="X141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>131</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Secretaría del H. Ayuntamiento de Morelia</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SecretariaAyuntamientoMorelia</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>30</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>15</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1</v>
+      </c>
+      <c r="X142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>132</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Secretaría de Desarrollo Urbano y Movilidad (Morelia)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DesarrolloUrbanoyMovilidad</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>30</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>15</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>1</v>
+      </c>
+      <c r="X143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>133</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Gobierno de Michoacán</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gobmichoacan</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>50</v>
+      </c>
+      <c r="L144" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>15</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>134</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SCOP Michoacán (obras estatales)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ScopMich</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>30</v>
+      </c>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>15</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>135</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Alarma Roja Morelia</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AFMMORELIA</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>50</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>15</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>136</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>El Sol de Morelia</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ElSolDemorelia.OEM</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>50</v>
+      </c>
+      <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>15</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>137</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LaPágina</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LaPaginaNoticias</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>30</v>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>15</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>138</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Molinero Vial Morelia</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/Molinero-Vial-Morelia/100063642935437/</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>50</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>15</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>139</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>La Nota Roja</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lanotarojamich</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>30</v>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>15</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>140</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Quadratín Michoacán</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/agenciaquadratin</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>50</v>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>15</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>141</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>MiMorelia.com</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mimoreliacom</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>50</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>15</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>142</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Post Data</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PostData.News</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>30</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>15</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>143</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ACG</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/agenciacomunicaciongrafica</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>30</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>1</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>15</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>144</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>morelia_descifra</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Canal 13 Michoacán</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Canal13Michoacan</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>30</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>15</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X155"/>
+  <dimension ref="A1:X186"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="19.6640625" customWidth="1" min="2" max="4"/>
@@ -1247,8 +1247,8 @@
       <c r="K11" t="n">
         <v>15</v>
       </c>
-      <c r="L11" t="b">
-        <v>1</v>
+      <c r="L11" t="n">
+        <v>0</v>
       </c>
       <c r="M11" t="b">
         <v>1</v>
@@ -1301,8 +1301,8 @@
       <c r="K12" t="n">
         <v>20</v>
       </c>
-      <c r="L12" t="b">
-        <v>1</v>
+      <c r="L12" t="n">
+        <v>0</v>
       </c>
       <c r="M12" t="b">
         <v>1</v>
@@ -1355,8 +1355,8 @@
       <c r="K13" t="n">
         <v>20</v>
       </c>
-      <c r="L13" t="b">
-        <v>1</v>
+      <c r="L13" t="n">
+        <v>0</v>
       </c>
       <c r="M13" t="b">
         <v>1</v>
@@ -1409,8 +1409,8 @@
       <c r="K14" t="n">
         <v>20</v>
       </c>
-      <c r="L14" t="b">
-        <v>1</v>
+      <c r="L14" t="n">
+        <v>0</v>
       </c>
       <c r="M14" t="b">
         <v>1</v>
@@ -1463,8 +1463,8 @@
       <c r="K15" t="n">
         <v>20</v>
       </c>
-      <c r="L15" t="b">
-        <v>1</v>
+      <c r="L15" t="n">
+        <v>0</v>
       </c>
       <c r="M15" t="b">
         <v>1</v>
@@ -1514,8 +1514,8 @@
       <c r="K16" t="n">
         <v>20</v>
       </c>
-      <c r="L16" t="b">
-        <v>1</v>
+      <c r="L16" t="n">
+        <v>0</v>
       </c>
       <c r="M16" t="b">
         <v>1</v>
@@ -1565,8 +1565,8 @@
       <c r="K17" t="n">
         <v>20</v>
       </c>
-      <c r="L17" t="b">
-        <v>1</v>
+      <c r="L17" t="n">
+        <v>0</v>
       </c>
       <c r="M17" t="b">
         <v>1</v>
@@ -1616,8 +1616,8 @@
       <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="L18" t="b">
-        <v>1</v>
+      <c r="L18" t="n">
+        <v>0</v>
       </c>
       <c r="M18" t="b">
         <v>1</v>
@@ -1667,8 +1667,8 @@
       <c r="K19" t="n">
         <v>5</v>
       </c>
-      <c r="L19" t="b">
-        <v>1</v>
+      <c r="L19" t="n">
+        <v>0</v>
       </c>
       <c r="M19" t="b">
         <v>1</v>
@@ -1718,8 +1718,8 @@
       <c r="K20" t="n">
         <v>20</v>
       </c>
-      <c r="L20" t="b">
-        <v>1</v>
+      <c r="L20" t="n">
+        <v>0</v>
       </c>
       <c r="M20" t="b">
         <v>1</v>
@@ -1769,8 +1769,8 @@
       <c r="K21" t="n">
         <v>30</v>
       </c>
-      <c r="L21" t="b">
-        <v>1</v>
+      <c r="L21" t="n">
+        <v>0</v>
       </c>
       <c r="M21" t="b">
         <v>1</v>
@@ -1820,8 +1820,8 @@
       <c r="K22" t="n">
         <v>50</v>
       </c>
-      <c r="L22" t="b">
-        <v>1</v>
+      <c r="L22" t="n">
+        <v>0</v>
       </c>
       <c r="M22" t="b">
         <v>1</v>
@@ -1871,8 +1871,8 @@
       <c r="K23" t="n">
         <v>25</v>
       </c>
-      <c r="L23" t="b">
-        <v>1</v>
+      <c r="L23" t="n">
+        <v>0</v>
       </c>
       <c r="M23" t="b">
         <v>1</v>
@@ -1973,8 +1973,8 @@
       <c r="K25" t="n">
         <v>30</v>
       </c>
-      <c r="L25" t="b">
-        <v>1</v>
+      <c r="L25" t="n">
+        <v>0</v>
       </c>
       <c r="M25" t="b">
         <v>1</v>
@@ -6141,8 +6141,8 @@
       <c r="K86" t="n">
         <v>20</v>
       </c>
-      <c r="L86" t="b">
-        <v>1</v>
+      <c r="L86" t="n">
+        <v>0</v>
       </c>
       <c r="M86" t="b">
         <v>1</v>
@@ -6195,8 +6195,8 @@
       <c r="K87" t="n">
         <v>20</v>
       </c>
-      <c r="L87" t="b">
-        <v>1</v>
+      <c r="L87" t="n">
+        <v>0</v>
       </c>
       <c r="M87" t="b">
         <v>1</v>
@@ -6249,8 +6249,8 @@
       <c r="K88" t="n">
         <v>20</v>
       </c>
-      <c r="L88" t="b">
-        <v>1</v>
+      <c r="L88" t="n">
+        <v>0</v>
       </c>
       <c r="M88" t="b">
         <v>1</v>
@@ -6303,8 +6303,8 @@
       <c r="K89" t="n">
         <v>50</v>
       </c>
-      <c r="L89" t="b">
-        <v>1</v>
+      <c r="L89" t="n">
+        <v>0</v>
       </c>
       <c r="M89" t="b">
         <v>1</v>
@@ -6354,8 +6354,8 @@
       <c r="K90" t="n">
         <v>50</v>
       </c>
-      <c r="L90" t="b">
-        <v>1</v>
+      <c r="L90" t="n">
+        <v>0</v>
       </c>
       <c r="M90" t="b">
         <v>1</v>
@@ -6415,8 +6415,8 @@
       <c r="K91" t="n">
         <v>50</v>
       </c>
-      <c r="L91" t="b">
-        <v>1</v>
+      <c r="L91" t="n">
+        <v>0</v>
       </c>
       <c r="M91" t="b">
         <v>1</v>
@@ -6479,8 +6479,8 @@
       <c r="K92" t="n">
         <v>50</v>
       </c>
-      <c r="L92" t="b">
-        <v>1</v>
+      <c r="L92" t="n">
+        <v>0</v>
       </c>
       <c r="M92" t="b">
         <v>1</v>
@@ -6540,8 +6540,8 @@
       <c r="K93" t="n">
         <v>100</v>
       </c>
-      <c r="L93" t="b">
-        <v>1</v>
+      <c r="L93" t="n">
+        <v>0</v>
       </c>
       <c r="M93" t="b">
         <v>1</v>
@@ -6614,8 +6614,8 @@
       <c r="K94" t="n">
         <v>100</v>
       </c>
-      <c r="L94" t="b">
-        <v>1</v>
+      <c r="L94" t="n">
+        <v>0</v>
       </c>
       <c r="M94" t="b">
         <v>1</v>
@@ -6661,8 +6661,8 @@
       <c r="K95" t="n">
         <v>100</v>
       </c>
-      <c r="L95" t="b">
-        <v>1</v>
+      <c r="L95" t="n">
+        <v>0</v>
       </c>
       <c r="M95" t="b">
         <v>1</v>
@@ -6725,8 +6725,8 @@
       <c r="K96" t="n">
         <v>100</v>
       </c>
-      <c r="L96" t="b">
-        <v>1</v>
+      <c r="L96" t="n">
+        <v>0</v>
       </c>
       <c r="M96" t="b">
         <v>1</v>
@@ -6794,8 +6794,8 @@
       <c r="K97" t="n">
         <v>200</v>
       </c>
-      <c r="L97" t="b">
-        <v>1</v>
+      <c r="L97" t="n">
+        <v>0</v>
       </c>
       <c r="M97" t="b">
         <v>1</v>
@@ -6858,8 +6858,8 @@
       <c r="K98" t="n">
         <v>10</v>
       </c>
-      <c r="L98" t="b">
-        <v>1</v>
+      <c r="L98" t="n">
+        <v>0</v>
       </c>
       <c r="M98" t="b">
         <v>1</v>
@@ -6910,8 +6910,8 @@
       <c r="K99" t="n">
         <v>10</v>
       </c>
-      <c r="L99" t="b">
-        <v>1</v>
+      <c r="L99" t="n">
+        <v>0</v>
       </c>
       <c r="M99" t="b">
         <v>1</v>
@@ -6962,8 +6962,8 @@
       <c r="K100" t="n">
         <v>10</v>
       </c>
-      <c r="L100" t="b">
-        <v>1</v>
+      <c r="L100" t="n">
+        <v>0</v>
       </c>
       <c r="M100" t="b">
         <v>1</v>
@@ -7017,8 +7017,8 @@
       <c r="K101" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L101" s="2" t="b">
-        <v>1</v>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="b">
         <v>1</v>
@@ -7070,8 +7070,8 @@
       <c r="K102" t="n">
         <v>100</v>
       </c>
-      <c r="L102" t="b">
-        <v>1</v>
+      <c r="L102" t="n">
+        <v>0</v>
       </c>
       <c r="M102" t="b">
         <v>1</v>
@@ -7134,8 +7134,8 @@
       <c r="K103" t="n">
         <v>50</v>
       </c>
-      <c r="L103" t="b">
-        <v>1</v>
+      <c r="L103" t="n">
+        <v>0</v>
       </c>
       <c r="M103" t="b">
         <v>1</v>
@@ -7193,8 +7193,8 @@
       <c r="K104" t="n">
         <v>100</v>
       </c>
-      <c r="L104" t="b">
-        <v>1</v>
+      <c r="L104" t="n">
+        <v>0</v>
       </c>
       <c r="M104" t="b">
         <v>1</v>
@@ -7267,8 +7267,8 @@
       <c r="K105" t="n">
         <v>150</v>
       </c>
-      <c r="L105" t="b">
-        <v>1</v>
+      <c r="L105" t="n">
+        <v>0</v>
       </c>
       <c r="M105" t="b">
         <v>1</v>
@@ -7336,8 +7336,8 @@
       <c r="K106" t="n">
         <v>150</v>
       </c>
-      <c r="L106" t="b">
-        <v>1</v>
+      <c r="L106" t="n">
+        <v>0</v>
       </c>
       <c r="M106" t="b">
         <v>1</v>
@@ -7394,8 +7394,8 @@
       <c r="K107" t="n">
         <v>150</v>
       </c>
-      <c r="L107" t="b">
-        <v>1</v>
+      <c r="L107" t="n">
+        <v>0</v>
       </c>
       <c r="M107" t="b">
         <v>1</v>
@@ -7468,8 +7468,8 @@
       <c r="K108" t="n">
         <v>150</v>
       </c>
-      <c r="L108" t="b">
-        <v>1</v>
+      <c r="L108" t="n">
+        <v>0</v>
       </c>
       <c r="M108" t="b">
         <v>1</v>
@@ -7526,8 +7526,8 @@
       <c r="K109" t="n">
         <v>150</v>
       </c>
-      <c r="L109" t="b">
-        <v>1</v>
+      <c r="L109" t="n">
+        <v>0</v>
       </c>
       <c r="M109" t="b">
         <v>1</v>
@@ -7600,8 +7600,8 @@
       <c r="K110" t="n">
         <v>150</v>
       </c>
-      <c r="L110" t="b">
-        <v>1</v>
+      <c r="L110" t="n">
+        <v>0</v>
       </c>
       <c r="M110" t="b">
         <v>1</v>
@@ -7658,8 +7658,8 @@
       <c r="K111" t="n">
         <v>150</v>
       </c>
-      <c r="L111" t="b">
-        <v>1</v>
+      <c r="L111" t="n">
+        <v>0</v>
       </c>
       <c r="M111" t="b">
         <v>1</v>
@@ -7725,8 +7725,8 @@
       <c r="K112" t="n">
         <v>20</v>
       </c>
-      <c r="L112" t="b">
-        <v>1</v>
+      <c r="L112" t="n">
+        <v>0</v>
       </c>
       <c r="M112" t="b">
         <v>1</v>
@@ -7797,8 +7797,8 @@
       <c r="K113" t="n">
         <v>20</v>
       </c>
-      <c r="L113" t="b">
-        <v>1</v>
+      <c r="L113" t="n">
+        <v>0</v>
       </c>
       <c r="M113" t="b">
         <v>1</v>
@@ -7869,8 +7869,8 @@
       <c r="K114" t="n">
         <v>20</v>
       </c>
-      <c r="L114" t="b">
-        <v>1</v>
+      <c r="L114" t="n">
+        <v>0</v>
       </c>
       <c r="M114" t="b">
         <v>1</v>
@@ -7941,8 +7941,8 @@
       <c r="K115" t="n">
         <v>15</v>
       </c>
-      <c r="L115" t="b">
-        <v>1</v>
+      <c r="L115" t="n">
+        <v>0</v>
       </c>
       <c r="M115" t="b">
         <v>1</v>
@@ -8013,8 +8013,8 @@
       <c r="K116" t="n">
         <v>15</v>
       </c>
-      <c r="L116" t="b">
-        <v>1</v>
+      <c r="L116" t="n">
+        <v>0</v>
       </c>
       <c r="M116" t="b">
         <v>1</v>
@@ -8085,8 +8085,8 @@
       <c r="K117" t="n">
         <v>15</v>
       </c>
-      <c r="L117" t="b">
-        <v>1</v>
+      <c r="L117" t="n">
+        <v>0</v>
       </c>
       <c r="M117" t="b">
         <v>1</v>
@@ -8157,8 +8157,8 @@
       <c r="K118" t="n">
         <v>20</v>
       </c>
-      <c r="L118" t="b">
-        <v>1</v>
+      <c r="L118" t="n">
+        <v>0</v>
       </c>
       <c r="M118" t="b">
         <v>1</v>
@@ -8229,8 +8229,8 @@
       <c r="K119" t="n">
         <v>15</v>
       </c>
-      <c r="L119" t="b">
-        <v>1</v>
+      <c r="L119" t="n">
+        <v>0</v>
       </c>
       <c r="M119" t="b">
         <v>1</v>
@@ -8301,8 +8301,8 @@
       <c r="K120" t="n">
         <v>20</v>
       </c>
-      <c r="L120" t="b">
-        <v>1</v>
+      <c r="L120" t="n">
+        <v>0</v>
       </c>
       <c r="M120" t="b">
         <v>1</v>
@@ -8375,8 +8375,8 @@
       <c r="K121" t="n">
         <v>100</v>
       </c>
-      <c r="L121" t="b">
-        <v>1</v>
+      <c r="L121" t="n">
+        <v>0</v>
       </c>
       <c r="M121" t="b">
         <v>1</v>
@@ -8446,8 +8446,8 @@
       <c r="K122" t="n">
         <v>50</v>
       </c>
-      <c r="L122" t="b">
-        <v>1</v>
+      <c r="L122" t="n">
+        <v>0</v>
       </c>
       <c r="M122" t="b">
         <v>1</v>
@@ -8515,8 +8515,8 @@
       <c r="K123" t="n">
         <v>50</v>
       </c>
-      <c r="L123" t="b">
-        <v>1</v>
+      <c r="L123" t="n">
+        <v>0</v>
       </c>
       <c r="M123" t="b">
         <v>1</v>
@@ -8584,8 +8584,8 @@
       <c r="K124" t="n">
         <v>50</v>
       </c>
-      <c r="L124" t="b">
-        <v>1</v>
+      <c r="L124" t="n">
+        <v>0</v>
       </c>
       <c r="M124" t="b">
         <v>1</v>
@@ -8648,8 +8648,8 @@
       <c r="K125" t="n">
         <v>50</v>
       </c>
-      <c r="L125" t="b">
-        <v>1</v>
+      <c r="L125" t="n">
+        <v>0</v>
       </c>
       <c r="M125" t="b">
         <v>1</v>
@@ -8712,8 +8712,8 @@
       <c r="K126" t="n">
         <v>50</v>
       </c>
-      <c r="L126" t="b">
-        <v>1</v>
+      <c r="L126" t="n">
+        <v>0</v>
       </c>
       <c r="M126" t="b">
         <v>1</v>
@@ -8870,8 +8870,8 @@
       <c r="K129" t="n">
         <v>20</v>
       </c>
-      <c r="L129" t="b">
-        <v>1</v>
+      <c r="L129" t="n">
+        <v>0</v>
       </c>
       <c r="M129" t="b">
         <v>1</v>
@@ -9240,7 +9240,7 @@
         <v>50</v>
       </c>
       <c r="L135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
         <v>1</v>
@@ -9423,7 +9423,7 @@
         <v>100</v>
       </c>
       <c r="L138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
         <v>1</v>
@@ -9477,7 +9477,7 @@
         <v>50</v>
       </c>
       <c r="L139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
         <v>1</v>
@@ -9531,7 +9531,7 @@
         <v>50</v>
       </c>
       <c r="L140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
         <v>1</v>
@@ -9585,7 +9585,7 @@
         <v>50</v>
       </c>
       <c r="L141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
         <v>1</v>
@@ -9639,7 +9639,7 @@
         <v>30</v>
       </c>
       <c r="L142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
         <v>1</v>
@@ -9693,7 +9693,7 @@
         <v>30</v>
       </c>
       <c r="L143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
         <v>1</v>
@@ -9747,7 +9747,7 @@
         <v>50</v>
       </c>
       <c r="L144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
         <v>1</v>
@@ -9798,7 +9798,7 @@
         <v>30</v>
       </c>
       <c r="L145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
         <v>1</v>
@@ -9849,7 +9849,7 @@
         <v>50</v>
       </c>
       <c r="L146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
         <v>1</v>
@@ -9900,7 +9900,7 @@
         <v>50</v>
       </c>
       <c r="L147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
         <v>1</v>
@@ -9951,7 +9951,7 @@
         <v>30</v>
       </c>
       <c r="L148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
         <v>1</v>
@@ -10002,7 +10002,7 @@
         <v>50</v>
       </c>
       <c r="L149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
         <v>1</v>
@@ -10053,7 +10053,7 @@
         <v>30</v>
       </c>
       <c r="L150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
         <v>1</v>
@@ -10104,7 +10104,7 @@
         <v>50</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
         <v>1</v>
@@ -10155,7 +10155,7 @@
         <v>50</v>
       </c>
       <c r="L152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
         <v>1</v>
@@ -10206,7 +10206,7 @@
         <v>30</v>
       </c>
       <c r="L153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
         <v>1</v>
@@ -10257,7 +10257,7 @@
         <v>30</v>
       </c>
       <c r="L154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
         <v>1</v>
@@ -10308,7 +10308,7 @@
         <v>30</v>
       </c>
       <c r="L155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
         <v>1</v>
@@ -10324,6 +10324,1748 @@
       </c>
       <c r="T155" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>145</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Informe de Gobierno Pinal de Amoles (keyword)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>pinal de amoles informe de gobierno</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>100</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>1</v>
+      </c>
+      <c r="N156" t="n">
+        <v>1</v>
+      </c>
+      <c r="O156" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre el Informe de Gobierno (V Informe) de la presidenta municipal de Pinal de Amoles, Querétaro, México, María Guadalupe «Lupita» Ramírez Plaza, o sobre las obras, programas y resultados que en él se informaron, y las reacciones a ese informe. Elimina informes de otros municipios o del gobierno del estado (por ejemplo el informe del gobernador Mauricio Kuri), promoción de negocios, ventas y publicaciones sin relación.</t>
+        </is>
+      </c>
+      <c r="S156" t="n">
+        <v>1</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>146</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Zitácuaro keyword</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>zitácuaro,zitacuaro</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>300</v>
+      </c>
+      <c r="L157" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" t="n">
+        <v>1</v>
+      </c>
+      <c r="N157" t="n">
+        <v>1</v>
+      </c>
+      <c r="O157" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Zitácuaro, Michoacán, México (seguridad, gobierno, obras, servicios, política, eventos, economía local). Elimina promoción de negocios, ventas, anuncios comerciales, saludos y publicaciones personales sin relevancia pública.</t>
+        </is>
+      </c>
+      <c r="S157" t="n">
+        <v>1</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>147</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Ayuntamiento de Zitácuaro</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ayuntamientozitacuaro</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>56421</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
+        <v>50</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="n">
+        <v>1</v>
+      </c>
+      <c r="N158" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" t="n">
+        <v>15</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>148</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Toño Ixtláhuac (alcalde)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/JAntonioIxtlahuac</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>50</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="n">
+        <v>15</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>149</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Es Zitácuaro</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EsZitacuaro</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>245471</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>20</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="n">
+        <v>1</v>
+      </c>
+      <c r="N160" t="n">
+        <v>1</v>
+      </c>
+      <c r="O160" t="n">
+        <v>15</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>150</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Digital Noticias Michoacán</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DigitalNoticiasMich</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>143255</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
+        <v>20</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
+        <v>1</v>
+      </c>
+      <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="n">
+        <v>15</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>151</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Marce Higareda de Paz</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/higaredadepaz</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>13099</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>15</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="n">
+        <v>1</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" t="n">
+        <v>15</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>152</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Diálogo Directo (Gilberto Silva)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dialogo.directo.79</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>16876</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>15</v>
+      </c>
+      <c r="L163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" t="n">
+        <v>1</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" t="n">
+        <v>15</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>153</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Evolución En Línea Michoacán</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EvolucionEnLineaMichoacan</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>3640</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
+        <v>15</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>1</v>
+      </c>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="n">
+        <v>15</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>154</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>El Clarín Diario de Zitácuaro</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/El-Clarin-Diario-de-Zit%C3%A1cuaro/100063494744425/</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>503</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K165" t="n">
+        <v>15</v>
+      </c>
+      <c r="L165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" t="n">
+        <v>1</v>
+      </c>
+      <c r="N165" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" t="n">
+        <v>15</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>155</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Periódico Milenio Zitácuaro</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/periodiconuevomileniomichoacan</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>30</v>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="n">
+        <v>1</v>
+      </c>
+      <c r="N166" t="n">
+        <v>1</v>
+      </c>
+      <c r="O166" t="n">
+        <v>15</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>156</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Zitácuaro en la Red Noticias</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100063548678123</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>30</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" t="n">
+        <v>1</v>
+      </c>
+      <c r="O167" t="n">
+        <v>15</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>157</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>El Despertar</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/periodicoeldespertar</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>30</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>1</v>
+      </c>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="n">
+        <v>15</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>158</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>zitacuaro</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Buscabullas Zitacuaro</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BuscabullasZ</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K169" t="n">
+        <v>30</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="n">
+        <v>15</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>159</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Pinal de Amoles keyword</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>pinal de amoles</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K170" t="n">
+        <v>100</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>1</v>
+      </c>
+      <c r="N170" t="n">
+        <v>1</v>
+      </c>
+      <c r="O170" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Pinal de Amoles, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+        </is>
+      </c>
+      <c r="S170" t="n">
+        <v>1</v>
+      </c>
+      <c r="T170" t="n">
+        <v>1</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>160</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Ayuntamiento de Pinal de Amoles (página oficial)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pinaldeamolesm</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K171" t="n">
+        <v>30</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="n">
+        <v>1</v>
+      </c>
+      <c r="O171" t="n">
+        <v>30</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>161</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Lupita Ramírez Plaza (presidenta)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LupitaRPlaza</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K172" t="n">
+        <v>30</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>1</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" t="n">
+        <v>30</v>
+      </c>
+      <c r="S172" t="n">
+        <v>0</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>162</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Iván Zárate (Inge Iván)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/IvanZarateM</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K173" t="n">
+        <v>40</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>1</v>
+      </c>
+      <c r="N173" t="n">
+        <v>1</v>
+      </c>
+      <c r="O173" t="n">
+        <v>30</v>
+      </c>
+      <c r="S173" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>163</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Fernando Sánchez Gil (Arroyo Seco)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/Fernando-S%C3%A1nchez/61558283724035/</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K174" t="n">
+        <v>30</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>1</v>
+      </c>
+      <c r="N174" t="n">
+        <v>1</v>
+      </c>
+      <c r="O174" t="n">
+        <v>30</v>
+      </c>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
+        <v>1</v>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>164</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Astrid Ortega (Cadereyta)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AstridOrtegaV/</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K175" t="n">
+        <v>30</v>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>1</v>
+      </c>
+      <c r="O175" t="n">
+        <v>30</v>
+      </c>
+      <c r="S175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>165</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Rubén Hernández (Jalpan)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Rub%C3%A9n-Hern%C3%A1ndez-61551688837412/</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>30</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="n">
+        <v>1</v>
+      </c>
+      <c r="N176" t="n">
+        <v>1</v>
+      </c>
+      <c r="O176" t="n">
+        <v>30</v>
+      </c>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
+        <v>1</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>166</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Yuni Benítez (Landa)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Yuni-Ben%C3%ADtez-61557467575264/</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K177" t="n">
+        <v>30</v>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>1</v>
+      </c>
+      <c r="N177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O177" t="n">
+        <v>30</v>
+      </c>
+      <c r="S177" t="n">
+        <v>0</v>
+      </c>
+      <c r="T177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>167</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Carlos Manuel Ledesma (San Joaquín)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CarlosManuelLedesmaRobleSj/</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K178" t="n">
+        <v>30</v>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N178" t="n">
+        <v>1</v>
+      </c>
+      <c r="O178" t="n">
+        <v>30</v>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
+        <v>1</v>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>168</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Blanca Benítez (diputada DL-15)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BlancaBenitezEstrada/</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K179" t="n">
+        <v>30</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>1</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1</v>
+      </c>
+      <c r="O179" t="n">
+        <v>30</v>
+      </c>
+      <c r="S179" t="n">
+        <v>0</v>
+      </c>
+      <c r="T179" t="n">
+        <v>1</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>169</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>facebook_page_posts</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Agustín Dorantes (senador)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AgustinDoran/</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>30</v>
+      </c>
+      <c r="L180" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" t="n">
+        <v>1</v>
+      </c>
+      <c r="N180" t="n">
+        <v>1</v>
+      </c>
+      <c r="O180" t="n">
+        <v>30</v>
+      </c>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>170</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Jalpan de Serra keyword</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>jalpan de serra</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K181" t="n">
+        <v>100</v>
+      </c>
+      <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
+        <v>1</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1</v>
+      </c>
+      <c r="O181" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Jalpan de Serra, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+        </is>
+      </c>
+      <c r="S181" t="n">
+        <v>1</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1</v>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>171</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Landa de Matamoros keyword</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>landa de matamoros</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
+        <v>100</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="n">
+        <v>1</v>
+      </c>
+      <c r="N182" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Landa de Matamoros, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+        </is>
+      </c>
+      <c r="S182" t="n">
+        <v>1</v>
+      </c>
+      <c r="T182" t="n">
+        <v>1</v>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>172</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Cadereyta de Montes keyword</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>cadereyta de montes</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K183" t="n">
+        <v>100</v>
+      </c>
+      <c r="L183" t="n">
+        <v>1</v>
+      </c>
+      <c r="M183" t="n">
+        <v>1</v>
+      </c>
+      <c r="N183" t="n">
+        <v>1</v>
+      </c>
+      <c r="O183" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Cadereyta de Montes, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+        </is>
+      </c>
+      <c r="S183" t="n">
+        <v>1</v>
+      </c>
+      <c r="T183" t="n">
+        <v>1</v>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>173</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Arroyo Seco keyword</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>arroyo seco querétaro</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K184" t="n">
+        <v>100</v>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
+        <v>1</v>
+      </c>
+      <c r="N184" t="n">
+        <v>1</v>
+      </c>
+      <c r="O184" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Arroyo Seco, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+        </is>
+      </c>
+      <c r="S184" t="n">
+        <v>1</v>
+      </c>
+      <c r="T184" t="n">
+        <v>1</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>174</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>San Joaquín keyword</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>san joaquín querétaro</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K185" t="n">
+        <v>100</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="n">
+        <v>1</v>
+      </c>
+      <c r="N185" t="n">
+        <v>1</v>
+      </c>
+      <c r="O185" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de San Joaquín, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+        </is>
+      </c>
+      <c r="S185" t="n">
+        <v>1</v>
+      </c>
+      <c r="T185" t="n">
+        <v>1</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>175</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>pinal_amoles</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Iván Zárate keyword</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>iván zárate</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K186" t="n">
+        <v>60</v>
+      </c>
+      <c r="L186" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" t="n">
+        <v>1</v>
+      </c>
+      <c r="N186" t="n">
+        <v>1</v>
+      </c>
+      <c r="O186" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre Iván Zárate Muñoz («Inge Iván»), presidente del DIF municipal de Pinal de Amoles, Querétaro, esposo de la presidenta municipal Lupita Ramírez Plaza: sus actividades, declaraciones y las reacciones a ellas. Elimina publicaciones sobre otras personas llamadas Iván Zárate.</t>
+        </is>
+      </c>
+      <c r="S186" t="n">
+        <v>1</v>
+      </c>
+      <c r="T186" t="n">
+        <v>1</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X186"/>
+  <dimension ref="A1:X183"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="19.6640625" customWidth="1" min="2" max="4"/>
@@ -1892,11 +1892,11 @@
     </row>
     <row r="24" hidden="1">
       <c r="A24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GROUPS</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Entérate Orizaba</t>
+          <t>Un Poco de Orizaba</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/enterateorizaba</t>
+          <t>https://www.facebook.com/unpocodeorizabaa</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1920,9 +1920,9 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>35</v>
-      </c>
-      <c r="L24" t="b">
+        <v>30</v>
+      </c>
+      <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="b">
@@ -1932,7 +1932,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -1942,27 +1942,39 @@
       </c>
     </row>
     <row r="25" hidden="1">
-      <c r="A25" t="n">
-        <v>18</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>instagram_hashtags</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>orizaba</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Un Poco de Orizaba</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/unpocodeorizabaa</t>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>chevron</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>es</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1971,49 +1983,71 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>30</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
       </c>
       <c r="M25" t="b">
         <v>1</v>
       </c>
       <c r="N25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Elimina las publicaciones que NO están relacionadas con lubricantes automotrices, aceites automotrices o mecánica automotriz. Elimina también las publicaciones cuando se pueda inferir que no se refieren a México</t>
+        </is>
       </c>
       <c r="S25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>{"keyword_search":false}</t>
+        </is>
       </c>
     </row>
     <row r="26" hidden="1">
-      <c r="A26" t="n">
-        <v>19</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GROUPS</t>
+          <t>instagram_hashtags</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>orizaba</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Balaceras Orizaba 2</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1233543673337523/</t>
+          <t>bp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>es</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2021,59 +2055,115 @@
           <t>w</t>
         </is>
       </c>
+      <c r="K26" t="n">
+        <v>20</v>
+      </c>
       <c r="L26" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Elimina las publicaciones que NO están relacionadas con lubricantes automotrices, aceites automotrices o mecánica automotriz. Elimina también las publicaciones cuando se pueda inferir que no se refieren a México</t>
+        </is>
       </c>
       <c r="S26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>{"keyword_search":false}</t>
+        </is>
       </c>
     </row>
     <row r="27" hidden="1">
-      <c r="A27" t="n">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>instagram_hashtags</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>totalenergies</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>British Petroleum</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>britishpetroleum</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
         <v>20</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>GROUPS</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>orizaba</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>balaceras y noticias sin censura “orizaba y zona centro de Veracruz”</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/386982481787894</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
       <c r="L27" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M27" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Elimina las publicaciones que NO están relacionadas con lubricantes automotrices, aceites automotrices o mecánica automotriz. Elimina también las publicaciones cuando se pueda inferir que no se refieren a México</t>
+        </is>
       </c>
       <c r="S27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>{"keyword_search":false}</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2088,12 +2178,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>EXXON MOBIL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>chevron</t>
+          <t>exxon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2146,7 +2236,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2161,12 +2251,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Castrol</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>castrol</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2219,7 +2309,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2234,12 +2324,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>British Petroleum</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>britishpetroleum</t>
+          <t>stp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2292,7 +2382,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2307,12 +2397,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EXXON MOBIL</t>
+          <t>Motul</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>exxon</t>
+          <t>motul</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2365,7 +2455,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2380,12 +2470,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Castrol</t>
+          <t>Alioth</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>castrol</t>
+          <t>alioth</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2404,7 +2494,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L32" t="b">
         <v>1</v>
@@ -2438,7 +2528,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2453,12 +2543,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>Mobil 1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stp</t>
+          <t>mobil1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2511,7 +2601,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2526,12 +2616,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Motul</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>motul</t>
+          <t>akron</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2584,7 +2674,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2599,12 +2689,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Alioth</t>
+          <t>Repsol</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>alioth</t>
+          <t>repsol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2623,7 +2713,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
@@ -2657,7 +2747,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2672,12 +2762,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mobil 1</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>mobil1</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2730,7 +2820,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2745,12 +2835,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Bardahl</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>akron</t>
+          <t>bardahl</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2803,12 +2893,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>instagram_hashtags</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2818,12 +2908,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Repsol</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>repsol</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2862,26 +2952,21 @@
         </is>
       </c>
       <c r="S38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="b">
         <v>0</v>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>{"keyword_search":false}</t>
-        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>instagram_hashtags</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2891,12 +2976,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>valvoline</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>valvoline</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2935,26 +3020,21 @@
         </is>
       </c>
       <c r="S39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" t="b">
         <v>0</v>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>{"keyword_search":false}</t>
-        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>instagram_hashtags</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2964,12 +3044,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bardahl</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>bardahl</t>
+          <t>chevron</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3008,21 +3088,16 @@
         </is>
       </c>
       <c r="S40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" t="b">
         <v>0</v>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>{"keyword_search":false}</t>
-        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3037,12 +3112,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>bp aceite</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3090,7 +3165,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3105,12 +3180,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>valvoline</t>
+          <t>British Petroleum</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>valvoline</t>
+          <t>"British Petroleum"</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3158,7 +3233,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3173,12 +3248,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>EXXON MOBIL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>chevron</t>
+          <t>exxon aceite</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3226,7 +3301,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3241,12 +3316,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Castrol</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>bp aceite</t>
+          <t>castrol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3294,7 +3369,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3309,12 +3384,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>British Petroleum</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>"British Petroleum"</t>
+          <t>aceite stp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3333,7 +3408,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -3362,7 +3437,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3377,12 +3452,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EXXON MOBIL</t>
+          <t>Motul</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>exxon aceite</t>
+          <t>aceite motul</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3430,7 +3505,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3445,12 +3520,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Castrol</t>
+          <t>Alioth</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>castrol</t>
+          <t>alioth</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3469,7 +3544,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -3498,7 +3573,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3513,12 +3588,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>Mobil 1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>aceite stp</t>
+          <t>"mobil 1"</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3537,7 +3612,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L48" t="b">
         <v>1</v>
@@ -3566,7 +3641,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3581,12 +3656,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Motul</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>aceite motul</t>
+          <t>akron aceite</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3634,7 +3709,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3649,12 +3724,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Alioth</t>
+          <t>Repsol</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>alioth</t>
+          <t>repsol</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3673,7 +3748,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -3702,7 +3777,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3717,12 +3792,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mobil 1</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>"mobil 1"</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3770,7 +3845,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3785,12 +3860,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Bardahl</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>akron aceite</t>
+          <t>bardahl</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3838,12 +3913,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>twitter_keyword_search</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3853,12 +3928,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Repsol</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>repsol</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3899,19 +3974,21 @@
       <c r="S53" t="b">
         <v>0</v>
       </c>
-      <c r="T53" t="b">
-        <v>0</v>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>twitter_keyword_search</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3921,12 +3998,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>valvoline</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>valvoline</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3967,19 +4044,21 @@
       <c r="S54" t="b">
         <v>0</v>
       </c>
-      <c r="T54" t="b">
-        <v>0</v>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>twitter_keyword_search</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3989,12 +4068,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Bardahl</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>bardahl</t>
+          <t>chevron</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4035,14 +4114,16 @@
       <c r="S55" t="b">
         <v>0</v>
       </c>
-      <c r="T55" t="b">
-        <v>0</v>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4057,12 +4138,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4112,7 +4193,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4127,12 +4208,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>valvoline</t>
+          <t>British Petroleum</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>valvoline</t>
+          <t>"British Petroleum"</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4182,7 +4263,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4197,12 +4278,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>EXXON MOBIL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>chevron</t>
+          <t>exxon aceite</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4252,7 +4333,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4267,12 +4348,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Castrol</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>castrol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4322,7 +4403,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4337,12 +4418,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>British Petroleum</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>"British Petroleum"</t>
+          <t>aceite stp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4392,7 +4473,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4407,12 +4488,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EXXON MOBIL</t>
+          <t>Motul</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>exxon aceite</t>
+          <t>aceite motul</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4462,7 +4543,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4477,12 +4558,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Castrol</t>
+          <t>Alioth</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>castrol</t>
+          <t>alioth</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4532,7 +4613,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4547,12 +4628,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>Mobil 1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>aceite stp</t>
+          <t>"mobil 1"</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4571,7 +4652,7 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -4602,7 +4683,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4617,12 +4698,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Motul</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>aceite motul</t>
+          <t>akron aceite</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4672,7 +4753,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4687,12 +4768,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Alioth</t>
+          <t>Repsol</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>alioth</t>
+          <t>repsol</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4742,7 +4823,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4757,12 +4838,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mobil 1</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>"mobil 1"</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4781,7 +4862,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L66" t="b">
         <v>1</v>
@@ -4812,7 +4893,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4827,12 +4908,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Bardahl</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>akron aceite</t>
+          <t>bardahl</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4882,12 +4963,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>twitter_keyword_search</t>
+          <t>linkedin_keyword_search</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4897,12 +4978,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Repsol</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>repsol</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4924,7 +5005,7 @@
         <v>20</v>
       </c>
       <c r="L68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="b">
         <v>1</v>
@@ -4943,21 +5024,19 @@
       <c r="S68" t="b">
         <v>0</v>
       </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="T68" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>twitter_keyword_search</t>
+          <t>linkedin_keyword_search</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4967,12 +5046,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>valvoline</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>valvoline</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4994,7 +5073,7 @@
         <v>20</v>
       </c>
       <c r="L69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="b">
         <v>1</v>
@@ -5013,21 +5092,19 @@
       <c r="S69" t="b">
         <v>0</v>
       </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="T69" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>twitter_keyword_search</t>
+          <t>linkedin_keyword_search</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5037,12 +5114,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Bardahl</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>bardahl</t>
+          <t>chevron</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5064,7 +5141,7 @@
         <v>20</v>
       </c>
       <c r="L70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="b">
         <v>1</v>
@@ -5083,16 +5160,14 @@
       <c r="S70" t="b">
         <v>0</v>
       </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="T70" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="71" hidden="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5107,12 +5182,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5160,7 +5235,7 @@
     <row r="72" hidden="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5175,12 +5250,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>valvoline</t>
+          <t>British Petroleum</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>valvoline</t>
+          <t>"British Petroleum"</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5228,7 +5303,7 @@
     <row r="73" hidden="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5243,12 +5318,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>EXXON MOBIL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>chevron</t>
+          <t>exxon</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5296,7 +5371,7 @@
     <row r="74" hidden="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5311,12 +5386,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Castrol</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>bp</t>
+          <t>castrol</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5364,7 +5439,7 @@
     <row r="75" hidden="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5379,12 +5454,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>British Petroleum</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>"British Petroleum"</t>
+          <t>stp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5432,7 +5507,7 @@
     <row r="76" hidden="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5447,12 +5522,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EXXON MOBIL</t>
+          <t>Motul</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>exxon</t>
+          <t>motul</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5500,7 +5575,7 @@
     <row r="77" hidden="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5515,12 +5590,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Castrol</t>
+          <t>Alioth</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>castrol</t>
+          <t>alioth</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5568,7 +5643,7 @@
     <row r="78" hidden="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5583,12 +5658,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>Mobil 1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stp</t>
+          <t>"mobil 1"</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5636,7 +5711,7 @@
     <row r="79" hidden="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5651,12 +5726,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Motul</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>motul</t>
+          <t>akron</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5704,7 +5779,7 @@
     <row r="80" hidden="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5719,12 +5794,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Alioth</t>
+          <t>Repsol</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>alioth</t>
+          <t>repsol</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5772,7 +5847,7 @@
     <row r="81" hidden="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5787,12 +5862,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mobil 1</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>"mobil 1"</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5840,7 +5915,7 @@
     <row r="82" hidden="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5855,12 +5930,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Bardahl</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>akron</t>
+          <t>bardahl</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5906,39 +5981,27 @@
       </c>
     </row>
     <row r="83" hidden="1">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="A83" t="n">
+        <v>80</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>linkedin_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>orizaba</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Repsol</t>
+          <t>Hugo Chahín Kuri</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>repsol</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>es</t>
+          <t>https://www.facebook.com/profile.php?id=100091646603729</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5949,65 +6012,51 @@
       <c r="K83" t="n">
         <v>20</v>
       </c>
-      <c r="L83" t="b">
+      <c r="L83" t="n">
         <v>0</v>
       </c>
       <c r="M83" t="b">
         <v>1</v>
       </c>
       <c r="N83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
         <v>15</v>
       </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Elimina las publicaciones que NO están relacionadas con lubricantes automotrices, aceites automotrices o mecánica automotriz. Elimina también las publicaciones cuando se pueda inferir que no se refieren a México</t>
-        </is>
-      </c>
       <c r="S83" t="b">
         <v>0</v>
       </c>
       <c r="T83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" hidden="1">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="A84" t="n">
+        <v>81</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>linkedin_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>queretaro</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Expreso Querétaro</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>shell</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
+          <t>https://www.facebook.com/profile.php?id=100064393401223</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>473000</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -6017,65 +6066,51 @@
       <c r="K84" t="n">
         <v>20</v>
       </c>
-      <c r="L84" t="b">
+      <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="b">
         <v>1</v>
       </c>
       <c r="N84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
         <v>15</v>
       </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Elimina las publicaciones que NO están relacionadas con lubricantes automotrices, aceites automotrices o mecánica automotriz. Elimina también las publicaciones cuando se pueda inferir que no se refieren a México</t>
-        </is>
-      </c>
       <c r="S84" t="b">
         <v>0</v>
       </c>
       <c r="T84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" hidden="1">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="A85" t="n">
+        <v>82</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>linkedin_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>queretaro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Bardahl</t>
+          <t>AlertaQro Noticias Querétaro</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>bardahl</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
+          <t>https://www.facebook.com/alertaqro</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1200000</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -6085,33 +6120,28 @@
       <c r="K85" t="n">
         <v>20</v>
       </c>
-      <c r="L85" t="b">
+      <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="b">
         <v>1</v>
       </c>
       <c r="N85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
         <v>15</v>
       </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Elimina las publicaciones que NO están relacionadas con lubricantes automotrices, aceites automotrices o mecánica automotriz. Elimina también las publicaciones cuando se pueda inferir que no se refieren a México</t>
-        </is>
-      </c>
       <c r="S85" t="b">
         <v>0</v>
       </c>
       <c r="T85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" hidden="1">
       <c r="A86" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -6120,18 +6150,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>orizaba</t>
+          <t>felifer</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Hugo Chahín Kuri</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/profile.php?id=100091646603729</t>
-        </is>
+          <t>FeliFer Macías</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/FeliferMaciasO</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>97000</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -6139,7 +6172,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -6162,11 +6195,11 @@
     </row>
     <row r="87" hidden="1">
       <c r="A87" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6176,16 +6209,13 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Expreso Querétaro</t>
+          <t>queretaro</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=100064393401223</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>473000</v>
+          <t>queretaro</t>
+        </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -6193,7 +6223,7 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -6207,39 +6237,46 @@
       <c r="O87" t="n">
         <v>15</v>
       </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el estado o ciudad de Querétaro (en general, temas que puedan ser de interés para el gobierno, ejemplo no exhaustivo: Emergencias, infraestructura, eventos culturales, servicios públicos, seguridad, ... entre otros). Elimina las preguntas de usuarios, ofertas de ventas, saludos, etc,)</t>
+        </is>
+      </c>
       <c r="S87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" t="b">
         <v>1</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
+        </is>
       </c>
     </row>
     <row r="88" hidden="1">
       <c r="A88" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>queretaro</t>
+          <t>felifer</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AlertaQro Noticias Querétaro</t>
+          <t>FeliFer Macías - Search</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/alertaqro</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>1200000</v>
+          <t>felifer</t>
+        </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -6247,7 +6284,7 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -6259,41 +6296,51 @@
         <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de querétaro Felifer Macías (Felipe Fernando Macías Olvera)</t>
+        </is>
       </c>
       <c r="S88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" t="b">
+        <v>1</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 34, "enrich_author_after_likes": 100}</t>
+        </is>
+      </c>
+      <c r="V88" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="89" hidden="1">
       <c r="A89" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>felifer</t>
+          <t>orizaba</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>FeliFer Macías</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/FeliferMaciasO</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>97000</v>
+          <t>Hugo Chahín Kuri - Search</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>chahin kuri</t>
+        </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6315,16 +6362,26 @@
       <c r="O89" t="n">
         <v>15</v>
       </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de orizaba Hugo Chahín Kuri</t>
+        </is>
+      </c>
       <c r="S89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" t="b">
         <v>1</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
+        </is>
       </c>
     </row>
     <row r="90" hidden="1">
       <c r="A90" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -6333,17 +6390,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>queretaro</t>
+          <t>zona_fest</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>queretaro</t>
+          <t>Zona Fest</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>queretaro</t>
+          <t>zona fest</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6352,7 +6409,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -6364,11 +6421,11 @@
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el estado o ciudad de Querétaro (en general, temas que puedan ser de interés para el gobierno, ejemplo no exhaustivo: Emergencias, infraestructura, eventos culturales, servicios públicos, seguridad, ... entre otros). Elimina las preguntas de usuarios, ofertas de ventas, saludos, etc,)</t>
+          <t>Conserva sólo las publicaciones que hablen del evento Zona Fest en Querétaro, o temas relacionados</t>
         </is>
       </c>
       <c r="S90" t="b">
@@ -6381,39 +6438,52 @@
         <is>
           <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
         </is>
+      </c>
+      <c r="V90" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="91" hidden="1">
       <c r="A91" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>google_news</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>felifer</t>
+          <t>zona_fest</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>FeliFer Macías - Search</t>
+          <t>Zona Fest</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>felifer</t>
+          <t>Zona Fest</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>es</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -6422,34 +6492,17 @@
         <v>1</v>
       </c>
       <c r="N91" t="b">
-        <v>1</v>
-      </c>
-      <c r="O91" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de querétaro Felifer Macías (Felipe Fernando Macías Olvera)</t>
-        </is>
-      </c>
-      <c r="S91" t="b">
-        <v>1</v>
-      </c>
-      <c r="T91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>{"get_comments_after_likes": 34, "enrich_author_after_likes": 100}</t>
-        </is>
-      </c>
-      <c r="V91" t="b">
-        <v>1</v>
+          <t>{"timeframe":"7d","enrich":true}</t>
+        </is>
       </c>
     </row>
     <row r="92" hidden="1">
       <c r="A92" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -6458,17 +6511,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>orizaba</t>
+          <t>zona_fest</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Hugo Chahín Kuri - Search</t>
+          <t>Zona Fest</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>chahin kuri</t>
+          <t>mexicozonafest</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6477,7 +6530,7 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -6489,11 +6542,11 @@
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de orizaba Hugo Chahín Kuri</t>
+          <t>Conserva sólo las publicaciones que hablen del evento Zona Fest en Querétaro, o temas relacionados</t>
         </is>
       </c>
       <c r="S92" t="b">
@@ -6506,11 +6559,14 @@
         <is>
           <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
         </is>
+      </c>
+      <c r="V92" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="93" hidden="1">
       <c r="A93" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -6529,7 +6585,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>zona fest</t>
+          <t>zonafest</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6574,11 +6630,11 @@
     </row>
     <row r="94" hidden="1">
       <c r="A94" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>google_news</t>
+          <t>tiktok_posts</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6593,7 +6649,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Zona Fest</t>
+          <t>zonafest</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6601,18 +6657,13 @@
           <t>_484</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -6621,45 +6672,62 @@
         <v>1</v>
       </c>
       <c r="N94" t="b">
-        <v>0</v>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>{"timeframe":"7d","enrich":true}</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="O94" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que hablen del evento Zona Fest en Querétaro, o temas relacionados (si menciona Zona Fest o variaciones y parece ser de México es muy probable que sí se refiera a este evento)</t>
+        </is>
+      </c>
+      <c r="S94" t="b">
+        <v>1</v>
+      </c>
+      <c r="T94" t="b">
+        <v>1</v>
+      </c>
+      <c r="V94" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="95" hidden="1">
       <c r="A95" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>google_news</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>zona_fest</t>
+          <t>top_news</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Zona Fest</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>mexicozonafest</t>
+          <t>Business News</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>es</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>d</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -6668,62 +6736,50 @@
         <v>1</v>
       </c>
       <c r="N95" t="b">
-        <v>1</v>
-      </c>
-      <c r="O95" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones que hablen del evento Zona Fest en Querétaro, o temas relacionados</t>
-        </is>
-      </c>
-      <c r="S95" t="b">
-        <v>1</v>
-      </c>
-      <c r="T95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
-        </is>
-      </c>
-      <c r="V95" t="b">
-        <v>1</v>
+          <t>{"timeframe":"1d","enrich":true, "topics": "BUSINESS"}</t>
+        </is>
       </c>
     </row>
     <row r="96" hidden="1">
       <c r="A96" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>google_news</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>zona_fest</t>
+          <t>top_news</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Zona Fest</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>zonafest</t>
+          <t>World News</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>es</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>d</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -6732,53 +6788,31 @@
         <v>1</v>
       </c>
       <c r="N96" t="b">
-        <v>1</v>
-      </c>
-      <c r="O96" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones que hablen del evento Zona Fest en Querétaro, o temas relacionados</t>
-        </is>
-      </c>
-      <c r="S96" t="b">
-        <v>1</v>
-      </c>
-      <c r="T96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
-        </is>
-      </c>
-      <c r="V96" t="b">
-        <v>1</v>
+          <t>{"timeframe":"1d","enrich":true, "topics": "WORLD"}</t>
+        </is>
       </c>
     </row>
     <row r="97" hidden="1">
       <c r="A97" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>tiktok_posts</t>
+          <t>google_news</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>zona_fest</t>
+          <t>top_news</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Zona Fest</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>zonafest</t>
+          <t>Nation News</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6786,13 +6820,18 @@
           <t>_484</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>d</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -6801,114 +6840,106 @@
         <v>1</v>
       </c>
       <c r="N97" t="b">
-        <v>1</v>
-      </c>
-      <c r="O97" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones que hablen del evento Zona Fest en Querétaro, o temas relacionados (si menciona Zona Fest o variaciones y parece ser de México es muy probable que sí se refiera a este evento)</t>
-        </is>
-      </c>
-      <c r="S97" t="b">
-        <v>1</v>
-      </c>
-      <c r="T97" t="b">
-        <v>1</v>
-      </c>
-      <c r="V97" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>{"timeframe":"1d","enrich":true, "topics": "NATION"}</t>
+        </is>
       </c>
     </row>
     <row r="98" hidden="1">
-      <c r="A98" t="n">
-        <v>92</v>
-      </c>
-      <c r="B98" t="inlineStr">
+      <c r="A98" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>google_news</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>top_news</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Business News</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Technology News</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>_484</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="I98" s="2" t="n"/>
+      <c r="J98" s="2" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="K98" t="n">
+      <c r="K98" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="b">
-        <v>1</v>
-      </c>
-      <c r="N98" t="b">
-        <v>0</v>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>{"timeframe":"1d","enrich":true, "topics": "BUSINESS"}</t>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O98" s="2" t="n"/>
+      <c r="P98" s="2" t="n"/>
+      <c r="Q98" s="2" t="n"/>
+      <c r="R98" s="2" t="n"/>
+      <c r="S98" s="2" t="n"/>
+      <c r="T98" s="2" t="n"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>{"timeframe":"1d","enrich":true, "topics": "TECHNOLOGY"}</t>
         </is>
       </c>
     </row>
     <row r="99" hidden="1">
       <c r="A99" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>google_news</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>top_news</t>
+          <t>chepe_guerrero</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>World News</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>es</t>
+          <t>Chepe Guerrero Search</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>chepe guerrero</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>w</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -6917,50 +6948,62 @@
         <v>1</v>
       </c>
       <c r="N99" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de corregidora, Chepe Guerrero (Josué David Guerrero)</t>
+        </is>
+      </c>
+      <c r="S99" t="b">
+        <v>1</v>
+      </c>
+      <c r="T99" t="b">
+        <v>1</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>{"timeframe":"1d","enrich":true, "topics": "WORLD"}</t>
-        </is>
+          <t>{"get_comments_after_likes": 34, "enrich_author_after_likes": 100}</t>
+        </is>
+      </c>
+      <c r="V99" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="100" hidden="1">
       <c r="A100" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>google_news</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>top_news</t>
+          <t>chepe_guerrero</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Nation News</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>es</t>
+          <t>Chepe Guerrero FB</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ChepeGro/</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>w</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -6969,78 +7012,93 @@
         <v>1</v>
       </c>
       <c r="N100" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O100" t="n">
+        <v>30</v>
+      </c>
+      <c r="S100" t="b">
+        <v>1</v>
+      </c>
+      <c r="T100" t="b">
+        <v>1</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>{"timeframe":"1d","enrich":true, "topics": "NATION"}</t>
-        </is>
+          <t>{"get_comments_after_likes": 34, "enrich_author_after_likes": 100}</t>
+        </is>
+      </c>
+      <c r="V100" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="101" hidden="1">
-      <c r="A101" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>google_news</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>top_news</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Technology News</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="n"/>
-      <c r="F101" s="2" t="n"/>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="n"/>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N101" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O101" s="2" t="n"/>
-      <c r="P101" s="2" t="n"/>
-      <c r="Q101" s="2" t="n"/>
-      <c r="R101" s="2" t="n"/>
-      <c r="S101" s="2" t="n"/>
-      <c r="T101" s="2" t="n"/>
-      <c r="U101" s="2" t="inlineStr">
-        <is>
-          <t>{"timeframe":"1d","enrich":true, "topics": "TECHNOLOGY"}</t>
-        </is>
+      <c r="A101" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>facebook_keyword_search</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>chepe_guerrero</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>David Guerrero Search</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>David Guerrero Corregidora</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>100</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="b">
+        <v>1</v>
+      </c>
+      <c r="N101" t="b">
+        <v>1</v>
+      </c>
+      <c r="O101" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de corregidora, Chepe Guerrero (Josué David Guerrero)</t>
+        </is>
+      </c>
+      <c r="S101" t="b">
+        <v>1</v>
+      </c>
+      <c r="T101" t="b">
+        <v>1</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 34, "enrich_author_after_likes": 100}</t>
+        </is>
+      </c>
+      <c r="V101" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="102" hidden="1">
       <c r="A102" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -7049,17 +7107,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>chepe_guerrero</t>
+          <t>efren_cuevas</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Chepe Guerrero Search</t>
+          <t>Efrén Cuevas</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>chepe guerrero</t>
+          <t>efren cuevas</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>es</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -7068,7 +7136,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -7077,15 +7145,10 @@
         <v>1</v>
       </c>
       <c r="N102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de corregidora, Chepe Guerrero (Josué David Guerrero)</t>
-        </is>
+        <v>25</v>
       </c>
       <c r="S102" t="b">
         <v>1</v>
@@ -7095,7 +7158,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>{"get_comments_after_likes": 34, "enrich_author_after_likes": 100}</t>
+          <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
         </is>
       </c>
       <c r="V102" t="b">
@@ -7104,7 +7167,7 @@
     </row>
     <row r="103" hidden="1">
       <c r="A103" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -7113,17 +7176,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>chepe_guerrero</t>
+          <t>mc</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Chepe Guerrero FB</t>
+          <t>Mariana Rodríguez FB</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ChepeGro/</t>
+          <t>https://www.facebook.com/marianardzcantu1</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>es</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7132,7 +7205,7 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -7144,18 +7217,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="n">
-        <v>30</v>
-      </c>
-      <c r="S103" t="b">
-        <v>1</v>
-      </c>
-      <c r="T103" t="b">
-        <v>1</v>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 34, "enrich_author_after_likes": 100}</t>
-        </is>
+        <v>25</v>
       </c>
       <c r="V103" t="b">
         <v>1</v>
@@ -7163,7 +7225,7 @@
     </row>
     <row r="104" hidden="1">
       <c r="A104" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -7172,17 +7234,27 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>chepe_guerrero</t>
+          <t>mc</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>David Guerrero Search</t>
+          <t>Mariana Rodríguez</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>David Guerrero Corregidora</t>
+          <t>Mariana Rodríguez</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>es</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7191,7 +7263,7 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -7203,11 +7275,11 @@
         <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de corregidora, Chepe Guerrero (Josué David Guerrero)</t>
+          <t>Conserva sólo las publicaciones que mencionen o hablen de Mariana Rodríguez, esposa del gobernador de Nuevo León, Samuel García y precandidata a la gubernatura de ese estado.</t>
         </is>
       </c>
       <c r="S104" t="b">
@@ -7218,7 +7290,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>{"get_comments_after_likes": 34, "enrich_author_after_likes": 100}</t>
+          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
         </is>
       </c>
       <c r="V104" t="b">
@@ -7227,26 +7299,26 @@
     </row>
     <row r="105" hidden="1">
       <c r="A105" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>efren_cuevas</t>
+          <t>mc</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Efrén Cuevas</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>efren cuevas</t>
+          <t>Colosio FB</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/colosioriojas</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7274,33 +7346,22 @@
         <v>1</v>
       </c>
       <c r="N105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105" t="n">
         <v>25</v>
       </c>
-      <c r="S105" t="b">
-        <v>1</v>
-      </c>
-      <c r="T105" t="b">
-        <v>1</v>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
-        </is>
-      </c>
       <c r="V105" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="106" hidden="1">
       <c r="A106" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7310,12 +7371,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mariana Rodríguez FB</t>
+          <t>Colosio</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marianardzcantu1</t>
+          <t>Luis Donaldo Colosio</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7348,17 +7409,33 @@
       <c r="O106" t="n">
         <v>25</v>
       </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que mencionen o hablen de Luis Donaldo Colosio Riojas, quien es un político mexicano, miembro del partido Movimiento Ciudadano. Actualmente es senador de la República y precandidato a la gobernatura de Sonora.</t>
+        </is>
+      </c>
+      <c r="S106" t="b">
+        <v>1</v>
+      </c>
+      <c r="T106" t="b">
+        <v>1</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
+        </is>
+      </c>
       <c r="V106" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="107" hidden="1">
       <c r="A107" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7368,12 +7445,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Mariana Rodríguez</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Mariana Rodríguez</t>
+          <t>Javier Lamarque FB</t>
+        </is>
+      </c>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/javierlamarquecano</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7406,33 +7483,17 @@
       <c r="O107" t="n">
         <v>25</v>
       </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones que mencionen o hablen de Mariana Rodríguez, esposa del gobernador de Nuevo León, Samuel García y precandidata a la gubernatura de ese estado.</t>
-        </is>
-      </c>
-      <c r="S107" t="b">
-        <v>1</v>
-      </c>
-      <c r="T107" t="b">
-        <v>1</v>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
-        </is>
-      </c>
       <c r="V107" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="108" hidden="1">
       <c r="A108" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7442,12 +7503,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Colosio FB</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/colosioriojas</t>
+          <t>Javier Lamarque</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Javier Lamarque</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7480,43 +7541,52 @@
       <c r="O108" t="n">
         <v>25</v>
       </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
+        </is>
+      </c>
+      <c r="S108" t="b">
+        <v>1</v>
+      </c>
+      <c r="T108" t="b">
+        <v>1</v>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
+        </is>
+      </c>
       <c r="V108" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="109" hidden="1">
       <c r="A109" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>mc</t>
+          <t>sjdr</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Colosio</t>
+          <t>El Sol de San Juan del Río</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Luis Donaldo Colosio</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
+          <t>https://www.facebook.com/ElSolDeSanJuan</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>487446</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -7524,7 +7594,7 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -7536,11 +7606,11 @@
         <v>1</v>
       </c>
       <c r="O109" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Conserva sólo las publicaciones que mencionen o hablen de Luis Donaldo Colosio Riojas, quien es un político mexicano, miembro del partido Movimiento Ciudadano. Actualmente es senador de la República y precandidato a la gobernatura de Sonora.</t>
+          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
         </is>
       </c>
       <c r="S109" t="b">
@@ -7556,11 +7626,16 @@
       </c>
       <c r="V109" t="b">
         <v>1</v>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="110" hidden="1">
       <c r="A110" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -7569,28 +7644,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>mc</t>
+          <t>sjdr</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Javier Lamarque FB</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/javierlamarquecano</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
+          <t>En La Mira</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EnLaMiraSanJuan</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>187824</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -7598,7 +7666,7 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -7610,45 +7678,59 @@
         <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>25</v>
+        <v>15</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
+        </is>
+      </c>
+      <c r="S110" t="b">
+        <v>1</v>
+      </c>
+      <c r="T110" t="b">
+        <v>1</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
+        </is>
       </c>
       <c r="V110" t="b">
         <v>1</v>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="111" hidden="1">
       <c r="A111" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>mc</t>
+          <t>sjdr</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Javier Lamarque</t>
+          <t>Noticias NR</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Javier Lamarque</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
+          <t>https://www.facebook.com/AlertasNR</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>108104</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7656,7 +7738,7 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -7668,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -7688,11 +7770,16 @@
       </c>
       <c r="V111" t="b">
         <v>1</v>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="112" hidden="1">
       <c r="A112" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -7706,16 +7793,16 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>El Sol de San Juan del Río</t>
+          <t>Despierta Tequis</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ElSolDeSanJuan</t>
+          <t>https://www.facebook.com/DespiertaTequis</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>487446</v>
+        <v>118222</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -7723,7 +7810,7 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -7764,7 +7851,7 @@
     </row>
     <row r="113" hidden="1">
       <c r="A113" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -7778,16 +7865,16 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>En La Mira</t>
+          <t>Pensador Queretano</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/EnLaMiraSanJuan</t>
+          <t>https://www.facebook.com/pensadorqueretano</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>187824</v>
+        <v>36836</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -7795,7 +7882,7 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -7836,7 +7923,7 @@
     </row>
     <row r="114" hidden="1">
       <c r="A114" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -7850,16 +7937,16 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Noticias NR</t>
+          <t>Informativo San Juan del Río</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/AlertasNR</t>
+          <t>https://www.facebook.com/InformativoSJR</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>108104</v>
+        <v>6930</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -7867,7 +7954,7 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -7908,7 +7995,7 @@
     </row>
     <row r="115" hidden="1">
       <c r="A115" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -7922,16 +8009,16 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Despierta Tequis</t>
+          <t>Presidencia Municipal San Juan del Río</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/DespiertaTequis</t>
+          <t>https://www.facebook.com/presidenciaSJR</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>118222</v>
+        <v>75673</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7939,7 +8026,7 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -7953,11 +8040,6 @@
       <c r="O115" t="n">
         <v>15</v>
       </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
-        </is>
-      </c>
       <c r="S115" t="b">
         <v>1</v>
       </c>
@@ -7973,6 +8055,11 @@
         <v>1</v>
       </c>
       <c r="W115" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -7980,7 +8067,7 @@
     </row>
     <row r="116" hidden="1">
       <c r="A116" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -7994,16 +8081,16 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Pensador Queretano</t>
+          <t>Cultura San Juan del Río</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/pensadorqueretano</t>
+          <t>https://www.facebook.com/CulturaSanJuandelRio</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>36836</v>
+        <v>14471</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -8025,11 +8112,6 @@
       <c r="O116" t="n">
         <v>15</v>
       </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
-        </is>
-      </c>
       <c r="S116" t="b">
         <v>1</v>
       </c>
@@ -8045,6 +8127,11 @@
         <v>1</v>
       </c>
       <c r="W116" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -8052,7 +8139,7 @@
     </row>
     <row r="117" hidden="1">
       <c r="A117" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -8066,16 +8153,16 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Informativo San Juan del Río</t>
+          <t>Roberto Cabrera</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/InformativoSJR</t>
+          <t>https://www.facebook.com/robertocabrerav</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>6930</v>
+        <v>58700</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -8083,7 +8170,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -8097,11 +8184,6 @@
       <c r="O117" t="n">
         <v>15</v>
       </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
-        </is>
-      </c>
       <c r="S117" t="b">
         <v>1</v>
       </c>
@@ -8117,6 +8199,11 @@
         <v>1</v>
       </c>
       <c r="W117" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -8124,11 +8211,11 @@
     </row>
     <row r="118" hidden="1">
       <c r="A118" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>tiktok_posts</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8138,24 +8225,26 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Presidencia Municipal San Juan del Río</t>
+          <t>San Juan del Río - TikTok</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/presidenciaSJR</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>75673</v>
+          <t>#sanjuandelrio,san juan del río</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K118" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -8164,31 +8253,28 @@
         <v>1</v>
       </c>
       <c r="N118" t="b">
-        <v>1</v>
-      </c>
-      <c r="O118" t="n">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
+        </is>
       </c>
       <c r="S118" t="b">
         <v>1</v>
       </c>
       <c r="T118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
+          <t>{"get_comments_after_likes": 100}</t>
         </is>
       </c>
       <c r="V118" t="b">
         <v>1</v>
       </c>
       <c r="W118" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -8196,11 +8282,11 @@
     </row>
     <row r="119" hidden="1">
       <c r="A119" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>tiktok_posts</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8210,24 +8296,26 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Cultura San Juan del Río</t>
+          <t>Roberto Cabrera - TikTok</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/CulturaSanJuandelRio</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>14471</v>
+          <t>roberto cabrera</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -8241,26 +8329,26 @@
       <c r="O119" t="n">
         <v>15</v>
       </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
+        </is>
+      </c>
       <c r="S119" t="b">
         <v>1</v>
       </c>
       <c r="T119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
+          <t>{"get_comments_after_likes": 100}</t>
         </is>
       </c>
       <c r="V119" t="b">
         <v>1</v>
       </c>
       <c r="W119" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -8268,7 +8356,7 @@
     </row>
     <row r="120" hidden="1">
       <c r="A120" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -8282,16 +8370,13 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Roberto Cabrera</t>
+          <t>Exa San Juan del Rio</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/robertocabrerav</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>58700</v>
+          <t>https://www.facebook.com/profile.php?id=61575923896715</t>
+        </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -8299,7 +8384,7 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -8313,6 +8398,11 @@
       <c r="O120" t="n">
         <v>15</v>
       </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
+        </is>
+      </c>
       <c r="S120" t="b">
         <v>1</v>
       </c>
@@ -8328,11 +8418,6 @@
         <v>1</v>
       </c>
       <c r="W120" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -8340,11 +8425,11 @@
     </row>
     <row r="121" hidden="1">
       <c r="A121" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tiktok_posts</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8354,26 +8439,21 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>San Juan del Río - TikTok</t>
+          <t>Bitacora Multimedios</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>#sanjuandelrio,san juan del río</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>_484</t>
+          <t>https://www.facebook.com/BitacoraDiario</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>w</t>
         </is>
       </c>
       <c r="K121" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -8382,7 +8462,10 @@
         <v>1</v>
       </c>
       <c r="N121" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O121" t="n">
+        <v>15</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -8393,12 +8476,7 @@
         <v>1</v>
       </c>
       <c r="T121" t="b">
-        <v>0</v>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 100}</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="V121" t="b">
         <v>1</v>
@@ -8411,11 +8489,11 @@
     </row>
     <row r="122" hidden="1">
       <c r="A122" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>tiktok_posts</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8425,22 +8503,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Roberto Cabrera - TikTok</t>
+          <t>Zona Radio</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>roberto cabrera</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>_484</t>
+          <t>https://www.facebook.com/ZonaRadio1053</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>w</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -8467,12 +8540,7 @@
         <v>1</v>
       </c>
       <c r="T122" t="b">
-        <v>0</v>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 100}</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="V122" t="b">
         <v>1</v>
@@ -8485,7 +8553,7 @@
     </row>
     <row r="123" hidden="1">
       <c r="A123" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -8499,12 +8567,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Exa San Juan del Rio</t>
+          <t>Voz Imparcial</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61575923896715</t>
+          <t>https://www.facebook.com/vozimparcialoficial</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8538,11 +8606,6 @@
       <c r="T123" t="b">
         <v>1</v>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
-        </is>
-      </c>
       <c r="V123" t="b">
         <v>1</v>
       </c>
@@ -8554,7 +8617,7 @@
     </row>
     <row r="124" hidden="1">
       <c r="A124" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8568,47 +8631,13 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Bitacora Multimedios</t>
+          <t>La Crónica Regional</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BitacoraDiario</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="K124" t="n">
-        <v>50</v>
-      </c>
-      <c r="L124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" t="b">
-        <v>1</v>
-      </c>
-      <c r="N124" t="b">
-        <v>1</v>
-      </c>
-      <c r="O124" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
-        </is>
-      </c>
-      <c r="S124" t="b">
-        <v>1</v>
-      </c>
-      <c r="T124" t="b">
-        <v>1</v>
-      </c>
-      <c r="V124" t="b">
-        <v>1</v>
+          <t>https://www.facebook.com/CronicaRegionalSJR</t>
+        </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
@@ -8618,11 +8647,11 @@
     </row>
     <row r="125" hidden="1">
       <c r="A125" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8632,23 +8661,18 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Zona Radio</t>
+          <t>Feria de SJdR</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ZonaRadio1053</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>w</t>
+          <t>feria san juan del rio</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>50</v>
-      </c>
-      <c r="L125" t="n">
+        <v>100</v>
+      </c>
+      <c r="L125" t="b">
         <v>0</v>
       </c>
       <c r="M125" t="b">
@@ -8662,7 +8686,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
+          <t>Conserva las publicaciones que hablen de la Feria de San Juan del Río, Querétaro 2026 o contenido relacionado</t>
         </is>
       </c>
       <c r="S125" t="b">
@@ -8670,6 +8694,11 @@
       </c>
       <c r="T125" t="b">
         <v>1</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
+        </is>
       </c>
       <c r="V125" t="b">
         <v>1</v>
@@ -8682,11 +8711,11 @@
     </row>
     <row r="126" hidden="1">
       <c r="A126" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8696,12 +8725,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Voz Imparcial</t>
+          <t>Roberto Cabrera - Search</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/vozimparcialoficial</t>
+          <t>Roberto Cabrera</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8710,7 +8739,7 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -8726,14 +8755,13 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el municipio de San Juan del Río, Querétaro, México (en general, temas que puedan ser de interés para el gobierno municipal, ejemplo no exhaustivo: emergencias, seguridad, accidentes, infraestructura, servicios públicos, política, obras, eventos cívicos y culturales, movilidad, entre otros). Elimina las publicaciones que se refieran a otros lugares llamados San Juan del Río (por ejemplo San Juan del Río en Oaxaca o Durango, o San Juan del Río Coco en Nicaragua). Elimina también la promoción o publicidad de negocios y comercios locales (restaurantes, cafés, tiendas, papelerías, gasolineras, inmobiliarias, gimnasios, etc.), los videos de humor o chisme sin tema de interés público, las preguntas de usuarios, ofertas de ventas y saludos. Elimina contenido de otros muncipios que no haga alusión a San Juan del Río</t>
-        </is>
-      </c>
-      <c r="S126" t="b">
-        <v>1</v>
-      </c>
-      <c r="T126" t="b">
-        <v>1</v>
+          <t>Conserva las publicaciones que mencionen o se refieran directa o indirectamente a Roberto Cabrera (Roberto Carlos Cabrera Valencia) Presidente municipal de San Juan del Río, Querétaro. Perteneciente al PAN. O sean contenido relacionado</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
+        </is>
       </c>
       <c r="V126" t="b">
         <v>1</v>
@@ -8745,38 +8773,74 @@
       </c>
     </row>
     <row r="127" hidden="1">
-      <c r="A127" t="n">
-        <v>121</v>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>gd1</t>
+        </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>google_news</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>sjdr</t>
+          <t>totalenergies_guadalupe</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>La Crónica Regional</t>
+          <t>Guadalupe seizure news</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/CronicaRegionalSJR</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>huachicol guadalupe</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>30</v>
+      </c>
+      <c r="L127" t="b">
+        <v>1</v>
+      </c>
+      <c r="M127" t="b">
+        <v>1</v>
+      </c>
+      <c r="N127" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>{"timeframe":"1d","enrich":true}</t>
         </is>
       </c>
     </row>
     <row r="128" hidden="1">
-      <c r="A128" t="n">
-        <v>122</v>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>gd2</t>
+        </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -8785,62 +8849,57 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>sjdr</t>
+          <t>totalenergies_guadalupe</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Feria de SJdR</t>
+          <t>Guadalupe seizure FB 1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>feria san juan del rio</t>
+          <t>huachicol guadalupe</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>w</t>
         </is>
       </c>
       <c r="K128" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="L128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" t="b">
         <v>1</v>
       </c>
       <c r="N128" t="b">
-        <v>1</v>
-      </c>
-      <c r="O128" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>Conserva las publicaciones que hablen de la Feria de San Juan del Río, Querétaro 2026 o contenido relacionado</t>
-        </is>
-      </c>
-      <c r="S128" t="b">
-        <v>1</v>
-      </c>
-      <c r="T128" t="b">
-        <v>1</v>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
-        </is>
-      </c>
-      <c r="V128" t="b">
-        <v>1</v>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
         </is>
       </c>
     </row>
     <row r="129" hidden="1">
-      <c r="A129" t="n">
-        <v>123</v>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>gd3</t>
+        </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -8849,17 +8908,27 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>sjdr</t>
+          <t>totalenergies_guadalupe</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Roberto Cabrera - Search</t>
+          <t>Guadalupe seizure FB 2</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Roberto Cabrera</t>
+          <t>huachicol nuevo león</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>_484</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>es</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8868,48 +8937,32 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>20</v>
-      </c>
-      <c r="L129" t="n">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="L129" t="b">
+        <v>1</v>
       </c>
       <c r="M129" t="b">
         <v>1</v>
       </c>
       <c r="N129" t="b">
-        <v>1</v>
-      </c>
-      <c r="O129" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Conserva las publicaciones que mencionen o se refieran directa o indirectamente a Roberto Cabrera (Roberto Carlos Cabrera Valencia) Presidente municipal de San Juan del Río, Querétaro. Perteneciente al PAN. O sean contenido relacionado</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
-        </is>
-      </c>
-      <c r="V129" t="b">
-        <v>1</v>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>gd1</t>
+          <t>gd4</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>google_news</t>
+          <t>twitter_keyword_search</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8919,12 +8972,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Guadalupe seizure news</t>
+          <t>Guadalupe seizure X 1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>huachicol guadalupe</t>
+          <t>huachicol,guadalupe</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8959,21 +9012,19 @@
           <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>{"timeframe":"1d","enrich":true}</t>
-        </is>
+      <c r="T130" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>gd2</t>
+          <t>gd5</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>twitter_keyword_search</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8983,12 +9034,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Guadalupe seizure FB 1</t>
+          <t>Guadalupe seizure X 2</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>huachicol guadalupe</t>
+          <t>huachicol,nuevo león</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9023,12 +9074,13 @@
           <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
         </is>
       </c>
+      <c r="T131" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>gd3</t>
-        </is>
+      <c r="A132" t="n">
+        <v>124</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -9037,207 +9089,209 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>totalenergies_guadalupe</t>
+          <t>orizaba</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Guadalupe seizure FB 2</t>
+          <t>El Chirimoyo - Search</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>huachicol nuevo león</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>es</t>
+          <t>el chirimoyo orizaba</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K132" t="n">
-        <v>30</v>
-      </c>
-      <c r="L132" t="b">
-        <v>1</v>
-      </c>
-      <c r="M132" t="b">
-        <v>1</v>
-      </c>
-      <c r="N132" t="b">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>1</v>
+      </c>
+      <c r="O132" t="n">
+        <v>15</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
+          <t>Conserva sólo las publicaciones que hablen del humedal, laguna o vaso regulador El Chirimoyo en Orizaba, Veracruz: su limpieza, el conflicto entre vecinos y el Ayuntamiento de Orizaba, amparos y resoluciones judiciales, Profepa, el lirio, la fauna o incidentes en el lugar. Elimina publicaciones sobre otros lugares llamados Chirimoyo (colonias o calles de otras ciudades) y las que mencionen Orizaba sin relación con El Chirimoyo.</t>
+        </is>
+      </c>
+      <c r="S132" t="n">
+        <v>1</v>
+      </c>
+      <c r="T132" t="n">
+        <v>1</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>{"enrich_author_after_likes": 50}</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>gd4</t>
-        </is>
+      <c r="A133" t="n">
+        <v>125</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>twitter_keyword_search</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>totalenergies_guadalupe</t>
+          <t>morelia_descifra</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Guadalupe seizure X 1</t>
+          <t>Morelia keyword (round 1, discovery)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>huachicol,guadalupe</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>es</t>
+          <t>morelia</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K133" t="n">
-        <v>30</v>
-      </c>
-      <c r="L133" t="b">
-        <v>1</v>
-      </c>
-      <c r="M133" t="b">
-        <v>1</v>
-      </c>
-      <c r="N133" t="b">
+        <v>1000</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
         <v>0</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
-        </is>
-      </c>
-      <c r="T133" t="b">
-        <v>1</v>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Morelia, Michoacán, México (seguridad, gobierno municipal o estatal, obras públicas, servicios como agua, basura, alumbrado, baches, movilidad y transporte, política y partidos, eventos y protestas, economía local, colonias y comunidades). Elimina: promoción de negocios, ventas y rentas, anuncios comerciales, saludos, publicaciones personales sin relevancia pública, y publicaciones que se refieran a otros lugares o cosas llamadas Morelia (calles llamadas Morelia en otras ciudades, el equipo de fútbol Atlético Morelia salvo que el tema sea de interés público local, Morelia como nombre de persona).</t>
+        </is>
+      </c>
+      <c r="S133" t="n">
+        <v>1</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>{"recent_posts": false, "enrich_author_after_likes": 100}</t>
+        </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>gd5</t>
-        </is>
+      <c r="A134" t="n">
+        <v>126</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>twitter_keyword_search</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>totalenergies_guadalupe</t>
+          <t>morelia_descifra</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Guadalupe seizure X 2</t>
+          <t>Morelia keyword variants (round 1c, discovery)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>huachicol,nuevo león</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>_484</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>es</t>
+          <t>morelia michoacán,ayuntamiento de morelia,gobierno de morelia,alfonso martínez morelia, morelia colonia,morelia baches,morelia agua,ooapas morelia,morelia obras, morelia seguridad,morelia policía,morelia transporte,morelia combis, morelia manifestación,morelia bloqueo,morelia bedolla,morelia morena,morelia pan, morelia tenencia,morelia alumbrado,morelia basura,morelia lluvias,morelia mercado, morelia vecinos,morelia centro histórico</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K134" t="n">
-        <v>30</v>
-      </c>
-      <c r="L134" t="b">
-        <v>1</v>
-      </c>
-      <c r="M134" t="b">
-        <v>1</v>
-      </c>
-      <c r="N134" t="b">
+        <v>100</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
         <v>0</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Elimina las publicaciones que NO están relacionadas con el aseguramiento de combustible ilegal (huachicol) en una bodega del municipio de Guadalupe, Nuevo León por parte de la FGR a finales de agosto de 2026. Elimina publicaciones que traten exclusivamente de otros decomisos u operativos, del caso de huachicol fiscal de Ernesto Ruffo, o de huachicol y política en general sin relación con este aseguramiento en Guadalupe.</t>
-        </is>
-      </c>
-      <c r="T134" t="b">
-        <v>1</v>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Morelia, Michoacán, México (seguridad, gobierno municipal o estatal, obras públicas, servicios como agua, basura, alumbrado, baches, movilidad y transporte, política y partidos, eventos y protestas, economía local, colonias y comunidades). Elimina: promoción de negocios, ventas y rentas, anuncios comerciales, saludos, publicaciones personales sin relevancia pública, y publicaciones que se refieran a otros lugares o cosas llamadas Morelia (calles llamadas Morelia en otras ciudades, el equipo de fútbol Atlético Morelia salvo que el tema sea de interés público local, Morelia como nombre de persona).</t>
+        </is>
+      </c>
+      <c r="S134" t="n">
+        <v>1</v>
+      </c>
+      <c r="T134" t="n">
+        <v>1</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>{"enrich_author_after_likes": 100}</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>orizaba</t>
+          <t>morelia_descifra</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>El Chirimoyo - Search</t>
+          <t>Gobierno de Morelia</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>el chirimoyo orizaba</t>
+          <t>https://www.facebook.com/MoreliaGob</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>w</t>
         </is>
       </c>
       <c r="K135" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -9246,35 +9300,28 @@
         <v>1</v>
       </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>15</v>
       </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones que hablen del humedal, laguna o vaso regulador El Chirimoyo en Orizaba, Veracruz: su limpieza, el conflicto entre vecinos y el Ayuntamiento de Orizaba, amparos y resoluciones judiciales, Profepa, el lirio, la fauna o incidentes en el lugar. Elimina publicaciones sobre otros lugares llamados Chirimoyo (colonias o calles de otras ciudades) y las que mencionen Orizaba sin relación con El Chirimoyo.</t>
-        </is>
-      </c>
       <c r="S135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T135" t="n">
         <v>1</v>
       </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>{"enrich_author_after_likes": 50}</t>
-        </is>
+      <c r="X135" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9284,21 +9331,21 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Morelia keyword (round 1, discovery)</t>
+          <t>Alfonso Martínez Alcázar (alcalde)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>morelia</t>
+          <t>https://www.facebook.com/AlfonsoMtz.Mx</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>w</t>
         </is>
       </c>
       <c r="K136" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -9310,32 +9357,25 @@
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Morelia, Michoacán, México (seguridad, gobierno municipal o estatal, obras públicas, servicios como agua, basura, alumbrado, baches, movilidad y transporte, política y partidos, eventos y protestas, economía local, colonias y comunidades). Elimina: promoción de negocios, ventas y rentas, anuncios comerciales, saludos, publicaciones personales sin relevancia pública, y publicaciones que se refieran a otros lugares o cosas llamadas Morelia (calles llamadas Morelia en otras ciudades, el equipo de fútbol Atlético Morelia salvo que el tema sea de interés público local, Morelia como nombre de persona).</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="S136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T136" t="n">
         <v>1</v>
       </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>{"recent_posts": false, "enrich_author_after_likes": 100}</t>
-        </is>
+      <c r="X136" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9345,21 +9385,21 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Morelia keyword variants (round 1c, discovery)</t>
+          <t>OOAPAS Morelia</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>morelia michoacán,ayuntamiento de morelia,gobierno de morelia,alfonso martínez morelia, morelia colonia,morelia baches,morelia agua,ooapas morelia,morelia obras, morelia seguridad,morelia policía,morelia transporte,morelia combis, morelia manifestación,morelia bloqueo,morelia bedolla,morelia morena,morelia pan, morelia tenencia,morelia alumbrado,morelia basura,morelia lluvias,morelia mercado, morelia vecinos,morelia centro histórico</t>
+          <t>https://www.facebook.com/MoreliaOoapas</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>w</t>
         </is>
       </c>
       <c r="K137" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -9371,28 +9411,21 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Morelia, Michoacán, México (seguridad, gobierno municipal o estatal, obras públicas, servicios como agua, basura, alumbrado, baches, movilidad y transporte, política y partidos, eventos y protestas, economía local, colonias y comunidades). Elimina: promoción de negocios, ventas y rentas, anuncios comerciales, saludos, publicaciones personales sin relevancia pública, y publicaciones que se refieran a otros lugares o cosas llamadas Morelia (calles llamadas Morelia en otras ciudades, el equipo de fútbol Atlético Morelia salvo que el tema sea de interés público local, Morelia como nombre de persona).</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="S137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
         <v>1</v>
       </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>{"enrich_author_after_likes": 100}</t>
-        </is>
+      <c r="X137" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -9406,12 +9439,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Gobierno de Morelia</t>
+          <t>Policía de Morelia</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MoreliaGob</t>
+          <t>https://www.facebook.com/policiademorelia</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9420,7 +9453,7 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -9446,7 +9479,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -9460,12 +9493,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Alfonso Martínez Alcázar (alcalde)</t>
+          <t>Secretaría del H. Ayuntamiento de Morelia</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/AlfonsoMtz.Mx</t>
+          <t>https://www.facebook.com/SecretariaAyuntamientoMorelia</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9474,7 +9507,7 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -9500,7 +9533,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -9514,12 +9547,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>OOAPAS Morelia</t>
+          <t>Secretaría de Desarrollo Urbano y Movilidad (Morelia)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/MoreliaOoapas</t>
+          <t>https://www.facebook.com/DesarrolloUrbanoyMovilidad</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9528,7 +9561,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -9554,7 +9587,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -9568,12 +9601,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Policía de Morelia</t>
+          <t>Gobierno de Michoacán</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/policiademorelia</t>
+          <t>https://www.facebook.com/gobmichoacan</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9602,13 +9635,10 @@
       <c r="T141" t="n">
         <v>1</v>
       </c>
-      <c r="X141" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -9622,12 +9652,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Secretaría del H. Ayuntamiento de Morelia</t>
+          <t>SCOP Michoacán (obras estatales)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/SecretariaAyuntamientoMorelia</t>
+          <t>https://www.facebook.com/ScopMich</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9656,13 +9686,10 @@
       <c r="T142" t="n">
         <v>1</v>
       </c>
-      <c r="X142" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -9676,12 +9703,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Secretaría de Desarrollo Urbano y Movilidad (Morelia)</t>
+          <t>Alarma Roja Morelia</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/DesarrolloUrbanoyMovilidad</t>
+          <t>https://www.facebook.com/AFMMORELIA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9690,7 +9717,7 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -9708,15 +9735,12 @@
         <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>1</v>
-      </c>
-      <c r="X143" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -9730,12 +9754,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Gobierno de Michoacán</t>
+          <t>El Sol de Morelia</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gobmichoacan</t>
+          <t>https://www.facebook.com/ElSolDemorelia.OEM</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9767,7 +9791,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -9781,12 +9805,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SCOP Michoacán (obras estatales)</t>
+          <t>LaPágina</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ScopMich</t>
+          <t>https://www.facebook.com/LaPaginaNoticias</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9818,7 +9842,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -9832,12 +9856,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Alarma Roja Morelia</t>
+          <t>Molinero Vial Morelia</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/AFMMORELIA</t>
+          <t>https://www.facebook.com/people/Molinero-Vial-Morelia/100063642935437/</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9869,7 +9893,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9883,12 +9907,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>El Sol de Morelia</t>
+          <t>La Nota Roja</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ElSolDemorelia.OEM</t>
+          <t>https://www.facebook.com/lanotarojamich</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9897,7 +9921,7 @@
         </is>
       </c>
       <c r="K147" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -9920,7 +9944,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -9934,12 +9958,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LaPágina</t>
+          <t>Quadratín Michoacán</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/LaPaginaNoticias</t>
+          <t>https://www.facebook.com/agenciaquadratin</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9948,7 +9972,7 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -9971,7 +9995,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -9985,12 +10009,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Molinero Vial Morelia</t>
+          <t>MiMorelia.com</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/people/Molinero-Vial-Morelia/100063642935437/</t>
+          <t>https://www.facebook.com/mimoreliacom</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -10022,7 +10046,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -10036,12 +10060,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>La Nota Roja</t>
+          <t>Post Data</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lanotarojamich</t>
+          <t>https://www.facebook.com/PostData.News</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -10073,7 +10097,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -10087,12 +10111,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Quadratín Michoacán</t>
+          <t>ACG</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agenciaquadratin</t>
+          <t>https://www.facebook.com/agenciacomunicaciongrafica</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -10101,7 +10125,7 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -10124,7 +10148,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -10138,12 +10162,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>MiMorelia.com</t>
+          <t>Canal 13 Michoacán</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mimoreliacom</t>
+          <t>https://www.facebook.com/Canal13Michoacan</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -10152,7 +10176,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -10175,77 +10199,87 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>morelia_descifra</t>
+          <t>pinal_amoles</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Post Data</t>
+          <t>Informe de Gobierno Pinal de Amoles (keyword)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/PostData.News</t>
+          <t>pinal de amoles informe de gobierno</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K153" t="n">
+        <v>100</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1</v>
+      </c>
+      <c r="N153" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" t="n">
         <v>30</v>
       </c>
-      <c r="L153" t="n">
-        <v>0</v>
-      </c>
-      <c r="M153" t="n">
-        <v>1</v>
-      </c>
-      <c r="N153" t="n">
-        <v>0</v>
-      </c>
-      <c r="O153" t="n">
-        <v>15</v>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre el Informe de Gobierno (V Informe) de la presidenta municipal de Pinal de Amoles, Querétaro, México, María Guadalupe «Lupita» Ramírez Plaza, o sobre las obras, programas y resultados que en él se informaron, y las reacciones a ese informe. Elimina informes de otros municipios o del gobierno del estado (por ejemplo el informe del gobernador Mauricio Kuri), promoción de negocios, ventas y publicaciones sin relación.</t>
+        </is>
       </c>
       <c r="S153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T153" t="n">
         <v>1</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>morelia_descifra</t>
+          <t>zitacuaro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ACG</t>
+          <t>Zitácuaro keyword</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agenciacomunicaciongrafica</t>
+          <t>zitácuaro,zitacuaro</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10254,30 +10288,40 @@
         </is>
       </c>
       <c r="K154" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" t="n">
         <v>1</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O154" t="n">
         <v>15</v>
       </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Zitácuaro, Michoacán, México (seguridad, gobierno, obras, servicios, política, eventos, economía local). Elimina promoción de negocios, ventas, anuncios comerciales, saludos y publicaciones personales sin relevancia pública.</t>
+        </is>
+      </c>
       <c r="S154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T154" t="n">
         <v>1</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -10286,18 +10330,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>morelia_descifra</t>
+          <t>zitacuaro</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Canal 13 Michoacán</t>
+          <t>Ayuntamiento de Zitácuaro</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Canal13Michoacan</t>
-        </is>
+          <t>https://www.facebook.com/ayuntamientozitacuaro</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>56421</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -10305,16 +10352,16 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" t="n">
         <v>1</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O155" t="n">
         <v>15</v>
@@ -10328,38 +10375,38 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>pinal_amoles</t>
+          <t>zitacuaro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Informe de Gobierno Pinal de Amoles (keyword)</t>
+          <t>Toño Ixtláhuac (alcalde)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>pinal de amoles informe de gobierno</t>
+          <t>https://www.facebook.com/JAntonioIxtlahuac</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>w</t>
         </is>
       </c>
       <c r="K156" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M156" t="n">
         <v>1</v>
@@ -10368,32 +10415,22 @@
         <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones sobre el Informe de Gobierno (V Informe) de la presidenta municipal de Pinal de Amoles, Querétaro, México, María Guadalupe «Lupita» Ramírez Plaza, o sobre las obras, programas y resultados que en él se informaron, y las reacciones a ese informe. Elimina informes de otros municipios o del gobierno del estado (por ejemplo el informe del gobernador Mauricio Kuri), promoción de negocios, ventas y publicaciones sin relación.</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="S156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T156" t="n">
         <v>1</v>
-      </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
-        </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10403,13 +10440,16 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Zitácuaro keyword</t>
+          <t>Es Zitácuaro</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>zitácuaro,zitacuaro</t>
-        </is>
+          <t>https://www.facebook.com/EsZitacuaro</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>245471</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -10417,7 +10457,7 @@
         </is>
       </c>
       <c r="K157" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="L157" t="n">
         <v>1</v>
@@ -10431,26 +10471,16 @@
       <c r="O157" t="n">
         <v>15</v>
       </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Zitácuaro, Michoacán, México (seguridad, gobierno, obras, servicios, política, eventos, economía local). Elimina promoción de negocios, ventas, anuncios comerciales, saludos y publicaciones personales sin relevancia pública.</t>
-        </is>
-      </c>
       <c r="S157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
         <v>1</v>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
-        </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -10464,16 +10494,16 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Ayuntamiento de Zitácuaro</t>
+          <t>Digital Noticias Michoacán</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ayuntamientozitacuaro</t>
+          <t>https://www.facebook.com/DigitalNoticiasMich</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>56421</v>
+        <v>143255</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -10481,7 +10511,7 @@
         </is>
       </c>
       <c r="K158" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L158" t="n">
         <v>1</v>
@@ -10504,7 +10534,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -10518,13 +10548,16 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Toño Ixtláhuac (alcalde)</t>
+          <t>Marce Higareda de Paz</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/JAntonioIxtlahuac</t>
-        </is>
+          <t>https://www.facebook.com/higaredadepaz</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>13099</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -10532,7 +10565,7 @@
         </is>
       </c>
       <c r="K159" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L159" t="n">
         <v>1</v>
@@ -10555,7 +10588,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -10569,16 +10602,16 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Es Zitácuaro</t>
+          <t>Diálogo Directo (Gilberto Silva)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/EsZitacuaro</t>
+          <t>https://www.facebook.com/dialogo.directo.79</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>245471</v>
+        <v>16876</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -10586,7 +10619,7 @@
         </is>
       </c>
       <c r="K160" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L160" t="n">
         <v>1</v>
@@ -10609,7 +10642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -10623,16 +10656,16 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Digital Noticias Michoacán</t>
+          <t>Evolución En Línea Michoacán</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/DigitalNoticiasMich</t>
+          <t>https://www.facebook.com/EvolucionEnLineaMichoacan</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>143255</v>
+        <v>3640</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -10640,7 +10673,7 @@
         </is>
       </c>
       <c r="K161" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
@@ -10663,7 +10696,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -10677,16 +10710,16 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Marce Higareda de Paz</t>
+          <t>El Clarín Diario de Zitácuaro</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/higaredadepaz</t>
+          <t>https://www.facebook.com/people/El-Clarin-Diario-de-Zit%C3%A1cuaro/100063494744425/</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>13099</v>
+        <v>503</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -10717,7 +10750,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -10731,16 +10764,13 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Diálogo Directo (Gilberto Silva)</t>
+          <t>Periódico Milenio Zitácuaro</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/dialogo.directo.79</t>
-        </is>
-      </c>
-      <c r="F163" t="n">
-        <v>16876</v>
+          <t>https://www.facebook.com/periodiconuevomileniomichoacan</t>
+        </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -10748,7 +10778,7 @@
         </is>
       </c>
       <c r="K163" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L163" t="n">
         <v>1</v>
@@ -10771,7 +10801,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -10785,16 +10815,13 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Evolución En Línea Michoacán</t>
+          <t>Zitácuaro en la Red Noticias</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/EvolucionEnLineaMichoacan</t>
-        </is>
-      </c>
-      <c r="F164" t="n">
-        <v>3640</v>
+          <t>https://www.facebook.com/profile.php?id=100063548678123</t>
+        </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -10802,7 +10829,7 @@
         </is>
       </c>
       <c r="K164" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
@@ -10825,7 +10852,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -10839,16 +10866,13 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>El Clarín Diario de Zitácuaro</t>
+          <t>El Despertar</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/people/El-Clarin-Diario-de-Zit%C3%A1cuaro/100063494744425/</t>
-        </is>
-      </c>
-      <c r="F165" t="n">
-        <v>503</v>
+          <t>https://www.facebook.com/periodicoeldespertar</t>
+        </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -10856,7 +10880,7 @@
         </is>
       </c>
       <c r="K165" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L165" t="n">
         <v>1</v>
@@ -10879,7 +10903,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -10893,12 +10917,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Periódico Milenio Zitácuaro</t>
+          <t>Buscabullas Zitacuaro</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/periodiconuevomileniomichoacan</t>
+          <t>https://www.facebook.com/BuscabullasZ</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10930,26 +10954,26 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>zitacuaro</t>
+          <t>pinal_amoles</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Zitácuaro en la Red Noticias</t>
+          <t>Pinal de Amoles keyword</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=100063548678123</t>
+          <t>pinal de amoles</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10958,30 +10982,40 @@
         </is>
       </c>
       <c r="K167" t="n">
+        <v>100</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" t="n">
+        <v>1</v>
+      </c>
+      <c r="O167" t="n">
         <v>30</v>
       </c>
-      <c r="L167" t="n">
-        <v>1</v>
-      </c>
-      <c r="M167" t="n">
-        <v>1</v>
-      </c>
-      <c r="N167" t="n">
-        <v>1</v>
-      </c>
-      <c r="O167" t="n">
-        <v>15</v>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Pinal de Amoles, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+        </is>
       </c>
       <c r="S167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T167" t="n">
         <v>1</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -10990,17 +11024,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>zitacuaro</t>
+          <t>pinal_amoles</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>El Despertar</t>
+          <t>Ayuntamiento de Pinal de Amoles (página oficial)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/periodicoeldespertar</t>
+          <t>https://www.facebook.com/pinaldeamolesm</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -11021,18 +11055,23 @@
         <v>1</v>
       </c>
       <c r="O168" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
       </c>
       <c r="T168" t="n">
         <v>1</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -11041,17 +11080,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>zitacuaro</t>
+          <t>pinal_amoles</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Buscabullas Zitacuaro</t>
+          <t>Lupita Ramírez Plaza (presidenta)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BuscabullasZ</t>
+          <t>https://www.facebook.com/LupitaRPlaza</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -11072,22 +11111,27 @@
         <v>1</v>
       </c>
       <c r="O169" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
       </c>
       <c r="T169" t="n">
         <v>1</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
+        </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>facebook_keyword_search</t>
+          <t>facebook_page_posts</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -11097,21 +11141,21 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Pinal de Amoles keyword</t>
+          <t>Iván Zárate (Inge Iván)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>pinal de amoles</t>
+          <t>https://www.facebook.com/IvanZarateM</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K170" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L170" t="n">
         <v>1</v>
@@ -11125,13 +11169,8 @@
       <c r="O170" t="n">
         <v>30</v>
       </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Pinal de Amoles, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
-        </is>
-      </c>
       <c r="S170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T170" t="n">
         <v>1</v>
@@ -11144,7 +11183,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -11158,17 +11197,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Ayuntamiento de Pinal de Amoles (página oficial)</t>
+          <t>Fernando Sánchez Gil (Arroyo Seco)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/pinaldeamolesm</t>
+          <t>https://www.facebook.com/people/Fernando-S%C3%A1nchez/61558283724035/</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K171" t="n">
@@ -11200,7 +11239,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -11214,17 +11253,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Lupita Ramírez Plaza (presidenta)</t>
+          <t>Astrid Ortega (Cadereyta)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/LupitaRPlaza</t>
+          <t>https://www.facebook.com/AstridOrtegaV/</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -11256,7 +11295,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -11270,12 +11309,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Iván Zárate (Inge Iván)</t>
+          <t>Rubén Hernández (Jalpan)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/IvanZarateM</t>
+          <t>https://www.facebook.com/p/Rub%C3%A9n-Hern%C3%A1ndez-61551688837412/</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11284,7 +11323,7 @@
         </is>
       </c>
       <c r="K173" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L173" t="n">
         <v>1</v>
@@ -11312,7 +11351,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -11326,12 +11365,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Fernando Sánchez Gil (Arroyo Seco)</t>
+          <t>Yuni Benítez (Landa)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/people/Fernando-S%C3%A1nchez/61558283724035/</t>
+          <t>https://www.facebook.com/p/Yuni-Ben%C3%ADtez-61557467575264/</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11368,7 +11407,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -11382,12 +11421,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Astrid Ortega (Cadereyta)</t>
+          <t>Carlos Manuel Ledesma (San Joaquín)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/AstridOrtegaV/</t>
+          <t>https://www.facebook.com/CarlosManuelLedesmaRobleSj/</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11424,7 +11463,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -11438,12 +11477,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Rubén Hernández (Jalpan)</t>
+          <t>Blanca Benítez (diputada DL-15)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Rub%C3%A9n-Hern%C3%A1ndez-61551688837412/</t>
+          <t>https://www.facebook.com/BlancaBenitezEstrada/</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11480,7 +11519,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11494,12 +11533,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Yuni Benítez (Landa)</t>
+          <t>Agustín Dorantes (senador)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Yuni-Ben%C3%ADtez-61557467575264/</t>
+          <t>https://www.facebook.com/AgustinDoran/</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11536,11 +11575,11 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11550,21 +11589,21 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Carlos Manuel Ledesma (San Joaquín)</t>
+          <t>Jalpan de Serra keyword</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/CarlosManuelLedesmaRobleSj/</t>
+          <t>jalpan de serra</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>w</t>
         </is>
       </c>
       <c r="K178" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="L178" t="n">
         <v>1</v>
@@ -11578,8 +11617,13 @@
       <c r="O178" t="n">
         <v>30</v>
       </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Jalpan de Serra, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+        </is>
+      </c>
       <c r="S178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T178" t="n">
         <v>1</v>
@@ -11592,11 +11636,11 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11606,21 +11650,21 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Blanca Benítez (diputada DL-15)</t>
+          <t>Landa de Matamoros keyword</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BlancaBenitezEstrada/</t>
+          <t>landa de matamoros</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>w</t>
         </is>
       </c>
       <c r="K179" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="L179" t="n">
         <v>1</v>
@@ -11634,8 +11678,13 @@
       <c r="O179" t="n">
         <v>30</v>
       </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Landa de Matamoros, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+        </is>
+      </c>
       <c r="S179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T179" t="n">
         <v>1</v>
@@ -11648,11 +11697,11 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>facebook_page_posts</t>
+          <t>facebook_keyword_search</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11662,21 +11711,21 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Agustín Dorantes (senador)</t>
+          <t>Cadereyta de Montes keyword</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/AgustinDoran/</t>
+          <t>cadereyta de montes</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>w</t>
         </is>
       </c>
       <c r="K180" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="L180" t="n">
         <v>1</v>
@@ -11690,8 +11739,13 @@
       <c r="O180" t="n">
         <v>30</v>
       </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Cadereyta de Montes, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+        </is>
+      </c>
       <c r="S180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T180" t="n">
         <v>1</v>
@@ -11704,7 +11758,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -11718,12 +11772,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Jalpan de Serra keyword</t>
+          <t>Arroyo Seco keyword</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>jalpan de serra</t>
+          <t>arroyo seco querétaro</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11748,7 +11802,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Jalpan de Serra, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Arroyo Seco, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
         </is>
       </c>
       <c r="S181" t="n">
@@ -11765,7 +11819,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -11779,12 +11833,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Landa de Matamoros keyword</t>
+          <t>San Joaquín keyword</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>landa de matamoros</t>
+          <t>san joaquín querétaro</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11809,7 +11863,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Landa de Matamoros, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de San Joaquín, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
         </is>
       </c>
       <c r="S182" t="n">
@@ -11826,7 +11880,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -11840,21 +11894,21 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes keyword</t>
+          <t>Iván Zárate keyword</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>cadereyta de montes</t>
+          <t>iván zárate</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K183" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L183" t="n">
         <v>1</v>
@@ -11870,7 +11924,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Cadereyta de Montes, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
+          <t>Conserva sólo las publicaciones sobre Iván Zárate Muñoz («Inge Iván»), presidente del DIF municipal de Pinal de Amoles, Querétaro, esposo de la presidenta municipal Lupita Ramírez Plaza: sus actividades, declaraciones y las reacciones a ellas. Elimina publicaciones sobre otras personas llamadas Iván Zárate.</t>
         </is>
       </c>
       <c r="S183" t="n">
@@ -11880,189 +11934,6 @@
         <v>1</v>
       </c>
       <c r="U183" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>173</v>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>facebook_keyword_search</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>pinal_amoles</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Arroyo Seco keyword</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>arroyo seco querétaro</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="K184" t="n">
-        <v>100</v>
-      </c>
-      <c r="L184" t="n">
-        <v>1</v>
-      </c>
-      <c r="M184" t="n">
-        <v>1</v>
-      </c>
-      <c r="N184" t="n">
-        <v>1</v>
-      </c>
-      <c r="O184" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de Arroyo Seco, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
-        </is>
-      </c>
-      <c r="S184" t="n">
-        <v>1</v>
-      </c>
-      <c r="T184" t="n">
-        <v>1</v>
-      </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>174</v>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>facebook_keyword_search</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>pinal_amoles</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>San Joaquín keyword</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>san joaquín querétaro</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="K185" t="n">
-        <v>100</v>
-      </c>
-      <c r="L185" t="n">
-        <v>1</v>
-      </c>
-      <c r="M185" t="n">
-        <v>1</v>
-      </c>
-      <c r="N185" t="n">
-        <v>1</v>
-      </c>
-      <c r="O185" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones sobre temas de interés público en el municipio de San Joaquín, en la Sierra Gorda de Querétaro, México, o en sus comunidades (seguridad, gobierno, obras, caminos, agua, servicios, programas, política, eventos, accidentes, clima, cultura). Elimina promoción de negocios, ventas, saludos, publicaciones personales sin relevancia pública y publicaciones sobre otros lugares con el mismo nombre.</t>
-        </is>
-      </c>
-      <c r="S185" t="n">
-        <v>1</v>
-      </c>
-      <c r="T185" t="n">
-        <v>1</v>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>175</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>facebook_keyword_search</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>pinal_amoles</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Iván Zárate keyword</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>iván zárate</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="K186" t="n">
-        <v>60</v>
-      </c>
-      <c r="L186" t="n">
-        <v>1</v>
-      </c>
-      <c r="M186" t="n">
-        <v>1</v>
-      </c>
-      <c r="N186" t="n">
-        <v>1</v>
-      </c>
-      <c r="O186" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>Conserva sólo las publicaciones sobre Iván Zárate Muñoz («Inge Iván»), presidente del DIF municipal de Pinal de Amoles, Querétaro, esposo de la presidenta municipal Lupita Ramírez Plaza: sus actividades, declaraciones y las reacciones a ellas. Elimina publicaciones sobre otras personas llamadas Iván Zárate.</t>
-        </is>
-      </c>
-      <c r="S186" t="n">
-        <v>1</v>
-      </c>
-      <c r="T186" t="n">
-        <v>1</v>
-      </c>
-      <c r="U186" t="inlineStr">
         <is>
           <t>{"get_comments_after_likes": 10, "enrich_author_after_likes": 30}</t>
         </is>
@@ -12085,11 +11956,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -10291,7 +10291,7 @@
         <v>300</v>
       </c>
       <c r="L154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
         <v>1</v>
@@ -10355,7 +10355,7 @@
         <v>50</v>
       </c>
       <c r="L155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
         <v>1</v>
@@ -10406,7 +10406,7 @@
         <v>50</v>
       </c>
       <c r="L156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
         <v>1</v>
@@ -10460,7 +10460,7 @@
         <v>20</v>
       </c>
       <c r="L157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
         <v>1</v>
@@ -10514,7 +10514,7 @@
         <v>20</v>
       </c>
       <c r="L158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
         <v>1</v>
@@ -10568,7 +10568,7 @@
         <v>15</v>
       </c>
       <c r="L159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
         <v>1</v>
@@ -10622,7 +10622,7 @@
         <v>15</v>
       </c>
       <c r="L160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
         <v>1</v>
@@ -10676,7 +10676,7 @@
         <v>15</v>
       </c>
       <c r="L161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
         <v>1</v>
@@ -10730,7 +10730,7 @@
         <v>15</v>
       </c>
       <c r="L162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
         <v>1</v>
@@ -10781,7 +10781,7 @@
         <v>30</v>
       </c>
       <c r="L163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
         <v>1</v>
@@ -10832,7 +10832,7 @@
         <v>30</v>
       </c>
       <c r="L164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
         <v>1</v>
@@ -10883,7 +10883,7 @@
         <v>30</v>
       </c>
       <c r="L165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
         <v>1</v>
@@ -10934,7 +10934,7 @@
         <v>30</v>
       </c>
       <c r="L166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
         <v>1</v>
@@ -10985,7 +10985,7 @@
         <v>100</v>
       </c>
       <c r="L167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
         <v>1</v>
@@ -11046,7 +11046,7 @@
         <v>30</v>
       </c>
       <c r="L168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
         <v>1</v>
@@ -11102,7 +11102,7 @@
         <v>30</v>
       </c>
       <c r="L169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
         <v>1</v>
@@ -11158,7 +11158,7 @@
         <v>40</v>
       </c>
       <c r="L170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
         <v>1</v>
@@ -11214,7 +11214,7 @@
         <v>30</v>
       </c>
       <c r="L171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
         <v>1</v>
@@ -11270,7 +11270,7 @@
         <v>30</v>
       </c>
       <c r="L172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
         <v>1</v>
@@ -11326,7 +11326,7 @@
         <v>30</v>
       </c>
       <c r="L173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
         <v>1</v>
@@ -11382,7 +11382,7 @@
         <v>30</v>
       </c>
       <c r="L174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
         <v>1</v>
@@ -11438,7 +11438,7 @@
         <v>30</v>
       </c>
       <c r="L175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
         <v>1</v>
@@ -11494,7 +11494,7 @@
         <v>30</v>
       </c>
       <c r="L176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
         <v>1</v>
@@ -11550,7 +11550,7 @@
         <v>30</v>
       </c>
       <c r="L177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
         <v>1</v>
@@ -11606,7 +11606,7 @@
         <v>100</v>
       </c>
       <c r="L178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
         <v>1</v>
@@ -11667,7 +11667,7 @@
         <v>100</v>
       </c>
       <c r="L179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
         <v>1</v>
@@ -11728,7 +11728,7 @@
         <v>100</v>
       </c>
       <c r="L180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
         <v>1</v>
@@ -11789,7 +11789,7 @@
         <v>100</v>
       </c>
       <c r="L181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
         <v>1</v>
@@ -11850,7 +11850,7 @@
         <v>100</v>
       </c>
       <c r="L182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
         <v>1</v>
@@ -11911,7 +11911,7 @@
         <v>60</v>
       </c>
       <c r="L183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
         <v>1</v>
